--- a/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
+++ b/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1747,299 +1747,291 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>GRC_THC7 : CBD1</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_GRC-II</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>GRC102501/1 7.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>High Pro Amnesia</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>HPA</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>HPA_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_HPA-I</t>
         </is>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F32" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G32" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H32" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I32" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>HPA1024_01 21.61, HPA052501 20.39</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr"/>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>HPA_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_HPA-II</t>
         </is>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F33" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G33" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H33" s="6" t="n">
         <v>19.79</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I33" s="6" t="n">
         <v>3.59</v>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>clipped (no-overlap rule)</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>HPA1024 17.31</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>JD</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>JD_THC20 : CBD1</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_JD-I</t>
         </is>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G34" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H34" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I34" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601 18.16</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>JD_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_JD-II</t>
         </is>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F35" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G35" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H35" s="6" t="n">
         <v>17.6</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I35" s="6" t="n">
         <v>3.2</v>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>JD012603/01 16.71, JD012603/02V 15.16</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Jokerz 31</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>J31</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>J31_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_J31-I</t>
         </is>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F36" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G36" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H36" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I36" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>J31122501 21.84, J31112501 20.21</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>J31_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_J31-II</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
-        <is>
-          <t>J31102501 17.32</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Kush Crasher</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>KC_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_KC-I</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -2049,31 +2041,31 @@
         <v>16.2</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>19.8</v>
+        <v>19.79</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>3.59</v>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>clipped (no-overlap rule)</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>KC102501 17.04</t>
+          <t>J31102501 17.32</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2083,165 +2075,173 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>MB_THC18 : CBD1</t>
+          <t>KC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-I</t>
+          <t>QCSP_001_KC-I</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
         <v>18</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>16.83</v>
+        <v>16.2</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>19.8</v>
       </c>
       <c r="I38" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>KC102501 17.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>MB_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_MB-I</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I39" s="6" t="n">
         <v>2.97</v>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>clipped (no-overlap rule)</t>
         </is>
       </c>
-      <c r="K38" s="8" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>MB0824_04 18.67</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>MB_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_MB-II</t>
         </is>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F40" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G40" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H40" s="6" t="n">
         <v>16.82</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I40" s="6" t="n">
         <v>2.42</v>
       </c>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>clipped (no-overlap rule)</t>
         </is>
       </c>
-      <c r="K39" s="8" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>MB0824_05 16.82</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>OPM</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>OPM_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_OPM-I</t>
         </is>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F41" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G41" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H41" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I41" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K40" s="8" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>OPM1024 20.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr"/>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>OPM_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_OPM-II</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>16.56</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>OPM1024_02 18.04</t>
         </is>
       </c>
     </row>
@@ -2250,30 +2250,30 @@
       <c r="B42" s="5" t="inlineStr"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-III</t>
+          <t>QCSP_001_OPM-II</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>14.4</v>
+        <v>16.56</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>16.55</v>
+        <v>19.79</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2.15</v>
+        <v>3.23</v>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
+          <t>OPM1024_02 18.04</t>
         </is>
       </c>
     </row>
@@ -2291,30 +2291,30 @@
       <c r="B43" s="5" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC14 : CBD1</t>
+          <t>OPM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-IV</t>
+          <t>QCSP_001_OPM-III</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>14.39</v>
+        <v>16.55</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>OPM052501 14.16</t>
+          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
         </is>
       </c>
     </row>
@@ -2332,39 +2332,39 @@
       <c r="B44" s="5" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC10 : CBD1</t>
+          <t>OPM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-V</t>
+          <t>QCSP_001_OPM-IV</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>11</v>
+        <v>14.39</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>1.79</v>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>clipped (no-overlap rule)</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>OPM092501 9.43</t>
+          <t>OPM052501 14.16</t>
         </is>
       </c>
     </row>
@@ -2373,129 +2373,129 @@
       <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>OPM_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_OPM-V</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>OPM092501 9.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_OPM-VI</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F46" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G46" s="6" t="n">
         <v>7.2</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H46" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I46" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>OPM112501 8.00, OPM122501 7.91</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>PM_THC14 : CBD1</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_PM-I</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F47" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G47" s="6" t="n">
         <v>12.6</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H47" s="6" t="n">
         <v>15.4</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I47" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K46" s="8" t="inlineStr">
+      <c r="K47" s="8" t="inlineStr">
         <is>
           <t>PM112501 13.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>PM_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_PM-II</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K47" s="8" t="inlineStr">
-        <is>
-          <t>PM092501 12.25</t>
         </is>
       </c>
     </row>
@@ -2504,27 +2504,27 @@
       <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>PM_THC10 : CBD1</t>
+          <t>PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-III</t>
+          <t>QCSP_001_PM-II</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>10.79</v>
+        <v>12.59</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>1.79</v>
@@ -2536,297 +2536,289 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
+          <t>PM092501 12.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr"/>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>PM_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_PM-III</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>clipped (no-overlap rule)</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
           <t>PM072501 10.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Pure Michigen</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>PUM</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>PUM_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_PUM-I</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="K49" s="8" t="inlineStr">
-        <is>
-          <t>PUM102501 15.63</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>PUM</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>PUM_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_PUM-I</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>PUM102501 15.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>SCR</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>SCR_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_SCR-I</t>
         </is>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F51" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G51" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H50" s="6" t="n">
+      <c r="H51" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I51" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K50" s="8" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
         <is>
           <t>SCR022601 21.92</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr"/>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr"/>
+      <c r="B52" s="5" t="inlineStr"/>
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_SCR-II</t>
         </is>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F52" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G52" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="H52" s="6" t="n">
         <v>19.79</v>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="I52" s="6" t="n">
         <v>3.59</v>
       </c>
-      <c r="J51" s="9" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>clipped (no-overlap rule)</t>
         </is>
       </c>
-      <c r="K51" s="8" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Sleepy Joy</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>SJ</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>SJ_THC12 : CBD1</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_SJ-I</t>
         </is>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F53" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G53" s="6" t="n">
         <v>10.97</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H53" s="6" t="n">
         <v>13.2</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I53" s="6" t="n">
         <v>2.23</v>
       </c>
-      <c r="J52" s="9" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>clipped (no-overlap rule)</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>SJ102501 11.20</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr"/>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr"/>
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>SJ_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_SJ-II</t>
         </is>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F54" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G53" s="6" t="n">
+      <c r="G54" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="H54" s="6" t="n">
         <v>10.96</v>
       </c>
-      <c r="I53" s="6" t="n">
+      <c r="I54" s="6" t="n">
         <v>1.96</v>
       </c>
-      <c r="J53" s="9" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>clipped (no-overlap rule)</t>
         </is>
       </c>
-      <c r="K53" s="8" t="inlineStr">
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>SJ092501 10.96, SJ112501 9.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Wedding Cake</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>WED</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>WED_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_WED-I</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="K54" s="8" t="inlineStr">
-        <is>
-          <t>WED102501 22.05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>WED</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -2836,12 +2828,12 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>WC_THC22 : CBD1</t>
+          <t>WED_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_WC-I</t>
+          <t>QCSP_001_WED-I</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -2862,6 +2854,55 @@
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>WED102501 22.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>WC_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_WC-I</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>WC072501 22.11, WC082501 21.67</t>
         </is>
@@ -2878,7 +2919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4728,43 +4769,47 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>HPA1024_01</t>
+          <t>GRC102501/1</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>HPA_THC22 : CBD1</t>
+          <t>GRC_THC7 : CBD1</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>21.61</v>
+        <v>7.05</v>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>197-14-К/26, 07.08.2026, FARM</t>
+          <t>owner-declared value</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>declared value — no eCoA yet, grade provisional until tested</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>HPA052501</t>
+          <t>HPA1024_01</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -4783,11 +4828,11 @@
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>20.39</v>
+        <v>21.61</v>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>ППК25278, 19.09.2025, UKIM</t>
+          <t>197-14-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -4800,7 +4845,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>HPA052501</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -4810,20 +4855,20 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>HPA_THC18 : CBD1</t>
+          <t>HPA_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>17.31</v>
+        <v>20.39</v>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>197-13-К/26, 07.08.2026, FARM</t>
+          <t>ППК25278, 19.09.2025, UKIM</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -4836,30 +4881,30 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>JD012603/02</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>JD_THC20 : CBD1</t>
+          <t>HPA_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>20.54</v>
+        <v>17.31</v>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, UKIM</t>
+          <t>197-13-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -4872,7 +4917,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>JD012603/02</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -4891,11 +4936,11 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>20.32</v>
+        <v>20.54</v>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>197-15-К/26, 07.08.2026, FARM</t>
+          <t>ППК26113, 30.06.2026, UKIM</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -4908,7 +4953,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -4927,28 +4972,24 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>18.58</v>
+        <v>20.32</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>ППК26115, 30.06.2026, UKIM</t>
+          <t>197-15-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>JD012601</t>
+          <t>JD022601</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -4967,11 +5008,11 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>18.16</v>
+        <v>18.58</v>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>ППК26064, 11.05.2026, UKIM</t>
+          <t>ППК26115, 30.06.2026, UKIM</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -4988,7 +5029,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>JD012603/01</t>
+          <t>JD012601</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
@@ -4998,37 +5039,37 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>JD_THC16 : CBD1</t>
+          <t>JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>16.71</v>
+        <v>18.16</v>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>ППК26064, 11.05.2026, UKIM</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>JD012603/02V</t>
+          <t>JD012603/01</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -5047,11 +5088,11 @@
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>15.16</v>
+        <v>16.71</v>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, UKIM</t>
+          <t>owner-declared value</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5059,52 +5100,52 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>declared value — no eCoA yet, grade provisional until tested</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>J31_THC22 : CBD1</t>
+          <t>JD_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>21.84</v>
+        <v>15.16</v>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>machine-trimmed preparation, CoQ-forming (CoQ-PP-2026-0054); hand-trimmed 19.84 is the experimental prep</t>
+          <t>ППК26111, 30.06.2026, UKIM</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>J31112501</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -5123,11 +5164,11 @@
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>20.21</v>
+        <v>21.84</v>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>100-1-K/26, 09.04.2026, FARM</t>
+          <t>machine-trimmed preparation, CoQ-forming (CoQ-PP-2026-0054); hand-trimmed 19.84 is the experimental prep</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5144,7 +5185,7 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>J31112501</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -5154,56 +5195,60 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>J31_THC18 : CBD1</t>
+          <t>J31_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>17.32</v>
+        <v>20.21</v>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>197-16-К/26, 07.08.2026, FARM</t>
+          <t>100-1-K/26, 09.04.2026, FARM</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H60" s="8" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>KC_THC18 : CBD1</t>
+          <t>J31_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>17.04</v>
+        <v>17.32</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>051-4-K/26, 04.03.2026, FARM</t>
+          <t>197-16-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -5216,12 +5261,12 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>MB0824_04</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5231,32 +5276,28 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>MB_THC18 : CBD1</t>
+          <t>KC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>18.67</v>
+        <v>17.04</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>ППК25118, 06.05.2025, UKIM</t>
+          <t>051-4-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>MB0824_05</t>
+          <t>MB0824_04</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -5266,56 +5307,60 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>MB_THC16 : CBD1</t>
+          <t>MB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>16.82</v>
+        <v>18.67</v>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>ППК52211, 28.07.2025, UKIM</t>
+          <t>ППК25118, 06.05.2025, UKIM</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>MB0824_05</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>OPM_THC22 : CBD1</t>
+          <t>MB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>20.03</v>
+        <v>16.82</v>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>197-17-К/26, 07.08.2026, FARM</t>
+          <t>ППК52211, 28.07.2025, UKIM</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -5328,7 +5373,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>OPM1024_02</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -5338,20 +5383,20 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>OPM_THC18 : CBD1</t>
+          <t>OPM_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>18.04</v>
+        <v>20.03</v>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>197-18-К/26, 07.08.2026, FARM</t>
+          <t>197-17-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -5364,7 +5409,7 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>OPM1024_03</t>
+          <t>OPM1024_02</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
@@ -5374,20 +5419,20 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>16.55</v>
+        <v>18.04</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>ППК25210, 28.07.2025, UKIM</t>
+          <t>197-18-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -5400,7 +5445,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>OMP1024_01</t>
+          <t>OPM1024_03</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -5419,11 +5464,11 @@
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>15.38</v>
+        <v>16.55</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>ППК25117, 06.05.2025, UKIM</t>
+          <t>ППК25210, 28.07.2025, UKIM</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -5436,7 +5481,7 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>OPM052501</t>
+          <t>OMP1024_01</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
@@ -5446,37 +5491,33 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>OPM_THC14 : CBD1</t>
+          <t>OPM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>14.16</v>
+        <v>15.38</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>ППК52557, 05.09.2025, UKIM</t>
+          <t>ППК25117, 06.05.2025, UKIM</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>OPM052501</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -5486,33 +5527,37 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>OPM_THC10 : CBD1</t>
+          <t>OPM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>9.43</v>
+        <v>14.16</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>ППК26008, 21.01.2026, UKIM</t>
+          <t>ППК52557, 05.09.2025, UKIM</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
@@ -5522,149 +5567,149 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>OPM_THC8 : CBD1</t>
+          <t>OPM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>8</v>
+        <v>9.43</v>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>ППК26031, 05.03.2026, UKIM</t>
+          <t>ППК26008, 21.01.2026, UKIM</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
+          <t>OPM112501</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>OPM_THC8 : CBD1</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>ППК26031, 05.03.2026, UKIM</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
           <t>OPM122501</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E72" s="6" t="n">
         <v>7.91</v>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>197-19-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>PM112501</t>
         </is>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
         <is>
           <t>PM_THC14 : CBD1</t>
         </is>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="E73" s="12" t="n">
         <v>13.33</v>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>ППК26030, 05.03.2026, UKIM</t>
         </is>
       </c>
-      <c r="G72" s="11" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>owner code THC12 infeasible for audited 13.33 — moved to THC14</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>PM092501</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Permanent Marker</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>PM_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>197-20-К/26, 07.08.2026, FARM</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>PM092501</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
@@ -5674,82 +5719,78 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>PM_THC10 : CBD1</t>
+          <t>PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>10.01</v>
+        <v>12.25</v>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>ППК25368, 28.11.2025, UKIM</t>
+          <t>197-20-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>PUM_THC16 : CBD1</t>
+          <t>PM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>15.63</v>
+        <v>10.01</v>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>ППК25368, 28.11.2025, UKIM</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -5759,32 +5800,32 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>SCR_THC22 : CBD1</t>
+          <t>PUM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>21.92</v>
+        <v>15.63</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, UKIM</t>
+          <t>owner-declared value</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+          <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>SCR012601</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -5794,20 +5835,20 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>SCR_THC18 : CBD1</t>
+          <t>SCR_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>18.07</v>
+        <v>21.92</v>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>ППК26116, 06.07.2026, UKIM</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -5817,14 +5858,14 @@
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>SCR012601</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
@@ -5843,24 +5884,28 @@
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>17.84</v>
+        <v>18.07</v>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>197-21-К/26, 07.08.2026, FARM</t>
+          <t>owner-declared value</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H78" s="8" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>declared value — no eCoA yet, grade provisional until tested</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -5879,11 +5924,11 @@
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>17.13</v>
+        <v>17.84</v>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>ППК26069, 11.05.2026, UKIM</t>
+          <t>197-21-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -5896,47 +5941,43 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>SJ102501</t>
+          <t>SCR112501</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>SJ_THC12 : CBD1</t>
+          <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>11.2</v>
+        <v>17.13</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>051-3-K/26, 04.03.2026, FARM</t>
+          <t>ППК26069, 11.05.2026, UKIM</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>SJ092501</t>
+          <t>SJ102501</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -5946,33 +5987,37 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>SJ_THC10 : CBD1</t>
+          <t>SJ_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>10.96</v>
+        <v>11.2</v>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>ППК26006, 21.01.2026, UKIM</t>
+          <t>051-3-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H81" s="8" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>SJ092501</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
@@ -5991,51 +6036,47 @@
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.96</v>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>051-2-K/26, 04.03.2026, FARM</t>
+          <t>ППК26006, 21.01.2026, UKIM</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>WED_THC22 : CBD1</t>
+          <t>SJ_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>22.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>051-2-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -6045,19 +6086,19 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>WC072501</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -6067,15 +6108,15 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>WC_THC22 : CBD1</t>
+          <t>WED_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>22.11</v>
+        <v>22.05</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>ППК25369, 28.11.2025, UKIM</t>
+          <t>owner-declared value</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -6085,45 +6126,85 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+          <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
+          <t>WC072501</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>WC_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>ППК25369, 28.11.2025, UKIM</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
           <t>WC082501</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Wedding Crasher</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>WC_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E86" s="6" t="n">
         <v>21.67</v>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>ППК26001, 21.01.2026, UKIM</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6136,7 +6217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6200,88 +6281,88 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ODD-nominal fallback (management rule, 27.08.2026): an isolated result that no even nominal can hold within ±10% (the even ladder has dead zones at 6.61–7.19 and 8.81–8.99) takes the adjacent ODD whole-number nominal instead, formed without overlap against the neighbouring ranges. With this fallback every result above ≈5.0% THC is always placeable (for any value v, at least one whole number lies between v/1.1 and v/0.9 once v ≥ 5).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>FLAGS</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme / GRC102501/1: 7.05 fits no even nominal (even-ladder dead zone) -&gt; ODD fallback THC7 [6.30-7.70]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Permanent Marker / PM112501: owner code THC12 infeasible for 13.33 (max window 10.80-13.20) -&gt; THC14</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>EXCEPTIONS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Graps &amp; Creme / GRC102501/1: 7.05 (declared (no eCoA yet)) fits NO even nominal within +/-10% — dead zone, excluded pending re-test</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>none — the odd-nominal fallback (rule 5) resolves all former dead-zone cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>OPEN VERIFICATIONS CARRIED OVER</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
-        </is>
-      </c>
+      <c r="B15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -6291,7 +6372,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
+          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6384,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6396,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
         </is>
       </c>
     </row>
@@ -6326,6 +6407,30 @@
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Batches on declared values (no eCoA yet): ACC102501, CC012603, CF102501, JD012603/01, PUM102501 (T2 re-analysis sampled 12.08.2026, results pending), SCR012601, WED102501, JD022601, GRC102501/1, P160012, P160022, P160032 — their grades are provisional.</t>
         </is>

--- a/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
+++ b/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -933,17 +933,17 @@
         <v>20</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>18</v>
+        <v>18.01</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>20</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC14 : CBD1</t>
+          <t>CJ_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -971,74 +971,66 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>12.6</v>
+        <v>16.2</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>15.4</v>
+        <v>18</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>1.8</v>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>CJ052501/02 14.93</t>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Cash Cow</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
+      <c r="A14" s="8" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>CC_THC18 : CBD1</t>
+          <t>CJ_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CC-I</t>
+          <t>QCSP_001_CJ-V</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>16.2</v>
+        <v>14.94</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>19.8</v>
+        <v>16.19</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>1.25</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>CC012601/1 17.67</t>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1039,17 @@
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>CC_THC14 : CBD1</t>
+          <t>CJ_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CC-II</t>
+          <t>QCSP_001_CJ-VI</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1067,379 +1059,379 @@
         <v>12.6</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>15.4</v>
+        <v>14.93</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+        <v>2.33</v>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>CJ052501/02 14.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>CC_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CC-I</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>CC012601/1 17.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>CC_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CC-II</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>RESERVE (contiguity bridge)</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>— reserve grade (no current batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CC_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CC-III</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>CC112501 13.35</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>CC_THC12 : CBD1</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC-III</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CC-IV</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H19" s="6" t="n">
         <v>12.59</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I19" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>CC012603 12.32</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Chem Flyer</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>CF_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_CF-I</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F20" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G20" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H20" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>CF102501 9.83</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Clemosa a bud</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>CLE_THC8 : CBD1</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_CLE-I</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G21" s="6" t="n">
         <v>7.2</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H21" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I21" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>CLE072501 8.02</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>FB_THC20 : CBD1</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_FB-I</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F22" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G22" s="6" t="n">
         <v>18.87</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H22" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I22" s="6" t="n">
         <v>3.13</v>
       </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>FB012603 20.83</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>FB_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_FB-II</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>FB_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_FB-III</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>FB012601/1 14.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>IV</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>FB_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_FB-IV</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>FB032601 12.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>GG</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>GG_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GG-I</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
         <v>18</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>16.71</v>
+        <v>16.2</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>19.8</v>
+        <v>18.86</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>3.09</v>
+        <v>2.66</v>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
+          <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
         </is>
       </c>
     </row>
@@ -1448,39 +1440,39 @@
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>GG_THC16 : CBD1</t>
+          <t>FB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-II</t>
+          <t>QCSP_001_FB-III</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
         <v>16</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>14.4</v>
+        <v>14.69</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>16.7</v>
+        <v>16.19</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>GG012603 16.70, GG1024_02 15.95, GG012601 15.35</t>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
@@ -1489,17 +1481,17 @@
       <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>GG_THC14 : CBD1</t>
+          <t>FB_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-III</t>
+          <t>QCSP_001_FB-IV</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -1509,109 +1501,109 @@
         <v>12.6</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>14.39</v>
+        <v>14.68</v>
       </c>
       <c r="I25" s="6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>FB012601/1 14.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>FB_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_FB-V</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="I26" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>GG1024 13.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>GP</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>FB032601 12.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>GP_THC24 : CBD1</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GP-I</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>GP_THC20 : CBD1</t>
+          <t>GG_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-II</t>
+          <t>QCSP_001_GG-I</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>18.53</v>
+        <v>16.71</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>21.59</v>
+        <v>19.8</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>GP072501/1 21.36, GP082501/1 21.29, GP0824_01 20.79, GP072501/2 19.81</t>
+          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
         </is>
       </c>
     </row>
@@ -1620,39 +1612,39 @@
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>GP_THC18 : CBD1</t>
+          <t>GG_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-III</t>
+          <t>QCSP_001_GG-II</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>16.2</v>
+        <v>14.4</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>18.52</v>
+        <v>16.7</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>GP052501 18.52</t>
+          <t>GG012603 16.70, GG1024_02 15.95, GG012601 15.35</t>
         </is>
       </c>
     </row>
@@ -1661,51 +1653,51 @@
       <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>GP_THC16 : CBD1</t>
+          <t>GG_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-IV</t>
+          <t>QCSP_001_GG-III</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>14.4</v>
+        <v>12.6</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>16.19</v>
+        <v>14.39</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>1.79</v>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>GP082501/2 15.70</t>
+          <t>GG1024 13.34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1715,25 +1707,25 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>GRC_THC12 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GRC-I</t>
+          <t>QCSP_001_GP-I</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>10.8</v>
+        <v>21.6</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>13.2</v>
+        <v>26.4</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
@@ -1742,7 +1734,7 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>GRC102501/2 11.53</t>
+          <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
         </is>
       </c>
     </row>
@@ -1756,83 +1748,75 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>GRC_THC7 : CBD1</t>
+          <t>GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GRC-II</t>
+          <t>QCSP_001_GP-II</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>6.3</v>
+        <v>18.53</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>7.7</v>
+        <v>21.59</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
+        <v>3.06</v>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>GRC102501/1 7.05</t>
+          <t>GP072501/1 21.36, GP082501/1 21.29, GP0824_01 20.79, GP072501/2 19.81</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>High Pro Amnesia</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>HPA</t>
-        </is>
-      </c>
+      <c r="A32" s="8" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>HPA_THC22 : CBD1</t>
+          <t>GP_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_HPA-I</t>
+          <t>QCSP_001_GP-III</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>19.8</v>
+        <v>16.2</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>24.2</v>
+        <v>18.52</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>2.32</v>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>HPA1024_01 21.61, HPA052501 20.39</t>
+          <t>GP052501 18.52</t>
         </is>
       </c>
     </row>
@@ -1841,51 +1825,51 @@
       <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>HPA_THC18 : CBD1</t>
+          <t>GP_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_HPA-II</t>
+          <t>QCSP_001_GP-IV</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>16.2</v>
+        <v>14.4</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>19.79</v>
+        <v>16.19</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>3.59</v>
+        <v>1.79</v>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>HPA1024 17.31</t>
+          <t>GP082501/2 15.70</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1895,25 +1879,25 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>JD_THC20 : CBD1</t>
+          <t>GRC_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-I</t>
+          <t>QCSP_001_GRC-I</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>18</v>
+        <v>10.8</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>22</v>
+        <v>13.2</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
@@ -1922,7 +1906,7 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601 18.16</t>
+          <t>GRC102501/2 11.53</t>
         </is>
       </c>
     </row>
@@ -1936,46 +1920,46 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>JD_THC16 : CBD1</t>
+          <t>GRC_THC7 : CBD1</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-II</t>
+          <t>QCSP_001_GRC-II</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>14.4</v>
+        <v>6.3</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>17.6</v>
+        <v>7.7</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>FULL ±10%</t>
+          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>JD012603/01 16.71, JD012603/02V 15.16</t>
+          <t>GRC102501/1 7.05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>J31</t>
+          <t>HPA</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1985,12 +1969,12 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>J31_THC22 : CBD1</t>
+          <t>HPA_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_J31-I</t>
+          <t>QCSP_001_HPA-I</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -2012,7 +1996,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>J31122501 21.84, J31112501 20.21</t>
+          <t>HPA1024_01 21.61, HPA052501 20.39</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2010,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>J31_THC18 : CBD1</t>
+          <t>HPA_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_J31-II</t>
+          <t>QCSP_001_HPA-II</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -2048,24 +2032,24 @@
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>J31102501 17.32</t>
+          <t>HPA1024 17.31</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2075,83 +2059,75 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>KC_THC18 : CBD1</t>
+          <t>JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_KC-I</t>
+          <t>QCSP_001_JD-I</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>16.2</v>
+        <v>18.01</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>3.99</v>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>KC102501 17.04</t>
+          <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601 18.16</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Motor Breath</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
+      <c r="A39" s="8" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>MB_THC18 : CBD1</t>
+          <t>JD_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-I</t>
+          <t>QCSP_001_JD-II</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
         <v>18</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>16.83</v>
+        <v>16.72</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>2.97</v>
+        <v>1.28</v>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>MB0824_04 18.67</t>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
@@ -2160,17 +2136,17 @@
       <c r="B40" s="5" t="inlineStr"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>MB_THC16 : CBD1</t>
+          <t>JD_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-II</t>
+          <t>QCSP_001_JD-III</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
@@ -2180,31 +2156,31 @@
         <v>14.4</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>16.82</v>
+        <v>16.71</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>MB0824_05 16.82</t>
+          <t>JD012603/01 16.71, JD012603/02V 15.16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>J31</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2214,12 +2190,12 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC22 : CBD1</t>
+          <t>J31_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-I</t>
+          <t>QCSP_001_J31-I</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
@@ -2241,7 +2217,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>OPM1024 20.03</t>
+          <t>J31122501 21.84, J31112501 20.21</t>
         </is>
       </c>
     </row>
@@ -2255,116 +2231,132 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC18 : CBD1</t>
+          <t>J31_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-II</t>
+          <t>QCSP_001_J31-II</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
         <v>18</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>16.56</v>
+        <v>16.2</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>19.79</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>3.23</v>
+        <v>3.59</v>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>OPM1024_02 18.04</t>
+          <t>J31102501 17.32</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr"/>
-      <c r="B43" s="5" t="inlineStr"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>KC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-III</t>
+          <t>QCSP_001_KC-I</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>16.55</v>
+        <v>19.8</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
+        <v>3.6</v>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
+          <t>KC102501 17.04</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC14 : CBD1</t>
+          <t>MB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-IV</t>
+          <t>QCSP_001_MB-I</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>12.6</v>
+        <v>16.83</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>14.39</v>
+        <v>19.8</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>1.79</v>
+        <v>2.97</v>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>OPM052501 14.16</t>
+          <t>MB0824_04 18.67</t>
         </is>
       </c>
     </row>
@@ -2373,129 +2365,129 @@
       <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC10 : CBD1</t>
+          <t>MB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-V</t>
+          <t>QCSP_001_MB-II</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>9</v>
+        <v>14.4</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>11</v>
+        <v>16.82</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
+        <v>2.42</v>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>MB0824_05 16.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>OPM_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_OPM-I</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
-        <is>
-          <t>OPM092501 9.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr"/>
-      <c r="B46" s="5" t="inlineStr"/>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>OPM_THC8 : CBD1</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_OPM-VI</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G46" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>OPM112501 8.00, OPM122501 7.91</t>
+          <t>OPM1024 20.03</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Permanent Marker</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
+      <c r="A47" s="8" t="inlineStr"/>
+      <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>PM_THC14 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-I</t>
+          <t>QCSP_001_OPM-II</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>12.6</v>
+        <v>16.56</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>15.4</v>
+        <v>19.79</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>3.23</v>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>PM112501 13.33</t>
+          <t>OPM1024_02 18.04</t>
         </is>
       </c>
     </row>
@@ -2504,39 +2496,39 @@
       <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>PM_THC12 : CBD1</t>
+          <t>OPM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-II</t>
+          <t>QCSP_001_OPM-III</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>10.8</v>
+        <v>14.4</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>12.59</v>
+        <v>16.55</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>PM092501 12.25</t>
+          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
         </is>
       </c>
     </row>
@@ -2545,137 +2537,121 @@
       <c r="B49" s="5" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>PM_THC10 : CBD1</t>
+          <t>OPM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-III</t>
+          <t>QCSP_001_OPM-IV</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>10.79</v>
+        <v>14.39</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>1.79</v>
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>clipped (no-overlap rule)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>PM072501 10.01</t>
+          <t>OPM052501 14.16</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Pure Michigen</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>PUM</t>
-        </is>
-      </c>
+      <c r="A50" s="8" t="inlineStr"/>
+      <c r="B50" s="5" t="inlineStr"/>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>PUM_THC16 : CBD1</t>
+          <t>OPM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PUM-I</t>
+          <t>QCSP_001_OPM-V</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>14.4</v>
+        <v>10.8</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>17.6</v>
+        <v>12.59</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>1.79</v>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>PUM102501 15.63</t>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>SCR</t>
-        </is>
-      </c>
+      <c r="A51" s="8" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SCR_THC22 : CBD1</t>
+          <t>OPM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_SCR-I</t>
+          <t>QCSP_001_OPM-VI</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>19.8</v>
+        <v>9</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>24.2</v>
+        <v>10.79</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>1.79</v>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>SCR022601 21.92</t>
+          <t>OPM092501 9.43</t>
         </is>
       </c>
     </row>
@@ -2684,51 +2660,51 @@
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>VII</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>SCR_THC18 : CBD1</t>
+          <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_SCR-II</t>
+          <t>QCSP_001_OPM-VII</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>16.2</v>
+        <v>7.2</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>19.79</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
+        <v>1.6</v>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
+          <t>OPM112501 8.00, OPM122501 7.91</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -2738,34 +2714,34 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>SJ_THC12 : CBD1</t>
+          <t>PM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_SJ-I</t>
+          <t>QCSP_001_PM-I</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>10.97</v>
+        <v>12.6</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>13.2</v>
+        <v>15.4</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
+        <v>2.8</v>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>SJ102501 11.20</t>
+          <t>PM112501 13.33</t>
         </is>
       </c>
     </row>
@@ -2779,130 +2755,400 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>SJ_THC10 : CBD1</t>
+          <t>PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_SJ-II</t>
+          <t>QCSP_001_PM-II</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>PM092501 12.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr"/>
+      <c r="B55" s="5" t="inlineStr"/>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>PM_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_PM-III</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="G55" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="H54" s="6" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>clipped (no-overlap rule)</t>
-        </is>
-      </c>
-      <c r="K54" s="8" t="inlineStr">
-        <is>
-          <t>SJ092501 10.96, SJ112501 9.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Wedding Cake</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>WED</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>WED_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_WED-I</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>19.8</v>
-      </c>
       <c r="H55" s="6" t="n">
-        <v>24.2</v>
+        <v>10.79</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+        <v>1.79</v>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>WED102501 22.05</t>
+          <t>PM072501 10.01</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>PUM</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>PUM_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_PUM-I</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>PUM102501 15.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>SCR</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>SCR_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SCR-I</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>SCR022601 21.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr"/>
+      <c r="B58" s="5" t="inlineStr"/>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>SCR_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SCR-II</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>SJ_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SJ-I</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>SJ102501 11.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>SJ_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SJ-II</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>SJ092501 10.96, SJ112501 9.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>WED</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>WED_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_WED-I</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>WED102501 22.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
           <t>Wedding Crasher</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>WC</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>WC_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_WC-I</t>
         </is>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F62" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G56" s="6" t="n">
+      <c r="G62" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H56" s="6" t="n">
+      <c r="H62" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I56" s="6" t="n">
+      <c r="I62" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="J62" s="7" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K56" s="8" t="inlineStr">
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>WC072501 22.11, WC082501 21.67</t>
         </is>
@@ -3515,7 +3761,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -3595,7 +3841,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -3635,7 +3881,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -3907,7 +4153,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -3943,7 +4189,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -5079,7 +5325,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -5119,7 +5365,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -5567,7 +5813,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -5603,7 +5849,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>VII</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -5643,7 +5889,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>VII</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -6217,7 +6463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6288,81 +6534,93 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ODD-nominal fallback (management rule, 27.08.2026): an isolated result that no even nominal can hold within ±10% (the even ladder has dead zones at 6.61–7.19 and 8.81–8.99) takes the adjacent ODD whole-number nominal instead, formed without overlap against the neighbouring ranges. With this fallback every result above ≈5.0% THC is always placeable (for any value v, at least one whole number lies between v/1.1 and v/0.9 once v ≥ 5).</t>
+          <t>Retest results are the CoQ-forming anchors (management rule, 27.08.2026): where a batch has a retest (Tranche 1 197-series of 07.08.2026, the April J31 retests, and the pending Tranche 2 re-analysis when it lands), the grade is designed on the retest value; superseded pre-retest results are out of specification scope.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Contiguity (management rule, 27.08.2026): from the top grade down, consecutive grade ranges join without gap or overlap (upper of the weaker = lower of the stronger minus 0.01). Where batch-bearing grades cannot join directly, RESERVE grades (spec-defined, no current batch) are inserted to close the span. Sole exception: below 10% THC, where the ladder mathematically cannot join, the lowest grade(s) may sit with a documented uncovered zone above them (GRC 7.71-10.79; OPM 8.81-8.99).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ODD-nominal fallback (management rule, 27.08.2026): an isolated result that no even nominal can hold within ±10% (the even ladder has dead zones at 6.61–7.19 and 8.81–8.99) takes the adjacent ODD whole-number nominal instead, formed without overlap against the neighbouring ranges. With this fallback every result above ≈5.0% THC is always placeable (for any value v, at least one whole number lies between v/1.1 and v/0.9 once v ≥ 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
           <t>FLAGS</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Graps &amp; Creme / GRC102501/1: 7.05 fits no even nominal (even-ladder dead zone) -&gt; ODD fallback THC7 [6.30-7.70]</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Permanent Marker / PM112501: owner code THC12 infeasible for 13.33 (max window 10.80-13.20) -&gt; THC14</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>EXCEPTIONS</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>none — the odd-nominal fallback (rule 5) resolves all former dead-zone cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>OPEN VERIFICATIONS CARRIED OVER</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme: uncovered zone 7.71-10.79 between THC12 and THC7 (sub-10% territory — even ladder cannot join; permitted per rule)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -6372,33 +6630,21 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
+          <t>Orange Punch Mimosa: uncovered zone 8.81-8.99 between THC10 and THC8 (sub-10% territory — even ladder cannot join; permitted per rule)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
-        </is>
-      </c>
+      <c r="A17" s="14" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
-        </is>
-      </c>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>OPEN VERIFICATIONS CARRIED OVER</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -6408,7 +6654,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
         </is>
       </c>
     </row>
@@ -6431,6 +6677,42 @@
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Batches on declared values (no eCoA yet): ACC102501, CC012603, CF102501, JD012603/01, PUM102501 (T2 re-analysis sampled 12.08.2026, results pending), SCR012601, WED102501, JD022601, GRC102501/1, P160012, P160022, P160032 — their grades are provisional.</t>
         </is>

--- a/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
+++ b/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
@@ -112,11 +112,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -506,11 +506,13 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="78" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="66" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,25 +562,35 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>Tolerance %</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>Lower %</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Upper %</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Width pp</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Potency expression</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Range status</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Batches (latest Total THC %)</t>
         </is>
@@ -613,21 +625,31 @@
       <c r="F5" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>±1.20</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>13.2</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>12.00% ±1.20% (10.80% — 13.20%)</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>ACC102501 12.91</t>
         </is>
@@ -662,21 +684,31 @@
       <c r="F6" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>±1.60</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="6" t="n">
         <v>17.6</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>3.2</v>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>AB092501 16.93</t>
         </is>
@@ -711,21 +743,31 @@
       <c r="F7" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>±2.60</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>23.4</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>28.6</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>5.2</v>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>26.00% ±2.60% (23.40% — 28.60%)</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>BG1024 26.14</t>
         </is>
@@ -760,28 +802,38 @@
       <c r="F8" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>±2.40</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>21.6</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>26.4</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>24.00% ±2.40% (21.60% — 26.40%)</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>BSS1024 25.01, BSS1024_01 23.42</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr"/>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -801,21 +853,31 @@
       <c r="F9" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>+1.59 / −2.00</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="6" t="n">
         <v>21.59</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>3.59</v>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>20.00% +1.59%/−2.00% (18.00% — 21.59%)</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>BSS052501 20.39</t>
         </is>
@@ -850,28 +912,38 @@
       <c r="F10" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>+2.40 / −1.99</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>22.01</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>26.4</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>4.39</v>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>24.00% +2.40%/−1.99% (22.01% — 26.40%)</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>CJ082501/1 24.96, CJ052501/01 24.05, CJ072501 23.70, CJ1024 23.00, CJ092501 22.30</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr"/>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -891,28 +963,38 @@
       <c r="F11" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>+0.00 / −1.99</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>20.01</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>1.99</v>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>22.00% +0.00%/−1.99% (20.01% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>CJ062501/1 21.51</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr"/>
+      <c r="A12" s="7" t="inlineStr"/>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -932,28 +1014,38 @@
       <c r="F12" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>+0.00 / −1.99</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>18.01</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>1.99</v>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>20.00% +0.00%/−1.99% (18.01% — 20.00%)</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>CJ062501/2 18.91, CJ082501/2 18.29</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -973,28 +1065,38 @@
       <c r="F13" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>+0.00 / −1.80</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +0.00%/−1.80% (16.20% — 18.00%)</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="7" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -1014,28 +1116,38 @@
       <c r="F14" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>+0.19 / −1.06</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>14.94</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="6" t="n">
         <v>16.19</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="J14" s="6" t="n">
         <v>1.25</v>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>16.00% +0.19%/−1.06% (14.94% — 16.19%)</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr"/>
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -1055,21 +1167,31 @@
       <c r="F15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>+0.93 / −1.40</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>12.6</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="6" t="n">
         <v>14.93</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>2.33</v>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>14.00% +0.93%/−1.40% (12.60% — 14.93%)</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>CJ052501/02 14.93</t>
         </is>
@@ -1104,28 +1226,38 @@
       <c r="F16" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>±1.80</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="J16" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>CC012601/1 17.67</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr"/>
+      <c r="A17" s="7" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -1145,28 +1277,38 @@
       <c r="F17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>+0.19 / −1.60</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="6" t="n">
         <v>16.19</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="J17" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>16.00% +0.19%/−1.60% (14.40% — 16.19%)</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr"/>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -1186,28 +1328,38 @@
       <c r="F18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>+0.39 / −1.40</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
         <v>12.6</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="6" t="n">
         <v>14.39</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="J18" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>14.00% +0.39%/−1.40% (12.60% — 14.39%)</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>CC112501 13.35</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr"/>
+      <c r="A19" s="7" t="inlineStr"/>
       <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -1227,21 +1379,31 @@
       <c r="F19" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>+0.59 / −1.20</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="6" t="n">
         <v>12.59</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="J19" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>12.00% +0.59%/−1.20% (10.80% — 12.59%)</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>CC012603 12.32</t>
         </is>
@@ -1276,21 +1438,31 @@
       <c r="F20" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="J20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>CF102501 9.83</t>
         </is>
@@ -1325,21 +1497,31 @@
       <c r="F21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>±0.80</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
         <v>7.2</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>CLE072501 8.02</t>
         </is>
@@ -1374,28 +1556,38 @@
       <c r="F22" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>+2.00 / −1.13</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
         <v>18.87</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="J22" s="6" t="n">
         <v>3.13</v>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>20.00% +2.00%/−1.13% (18.87% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>FB012603 20.83</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr"/>
+      <c r="A23" s="7" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
@@ -1415,28 +1607,38 @@
       <c r="F23" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>+0.86 / −1.80</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>18.86</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>2.66</v>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +0.86%/−1.80% (16.20% — 18.86%)</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr"/>
+      <c r="A24" s="7" t="inlineStr"/>
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
@@ -1456,28 +1658,38 @@
       <c r="F24" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>+0.19 / −1.31</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>14.69</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>16.19</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>16.00% +0.19%/−1.31% (14.69% — 16.19%)</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr"/>
+      <c r="A25" s="7" t="inlineStr"/>
       <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -1497,28 +1709,38 @@
       <c r="F25" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>+0.68 / −1.40</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>12.6</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>14.68</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>2.08</v>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>14.00% +0.68%/−1.40% (12.60% — 14.68%)</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>FB012601/1 14.68</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr"/>
+      <c r="A26" s="7" t="inlineStr"/>
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
@@ -1538,21 +1760,31 @@
       <c r="F26" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>+0.59 / −1.20</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="6" t="n">
         <v>12.59</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>12.00% +0.59%/−1.20% (10.80% — 12.59%)</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>FB032601 12.39</t>
         </is>
@@ -1587,28 +1819,38 @@
       <c r="F27" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>+1.80 / −1.29</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>16.71</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>3.09</v>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +1.80%/−1.29% (16.71% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr"/>
+      <c r="A28" s="7" t="inlineStr"/>
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -1628,28 +1870,38 @@
       <c r="F28" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>+0.70 / −1.60</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="J28" s="6" t="n">
         <v>2.3</v>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>16.00% +0.70%/−1.60% (14.40% — 16.70%)</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>GG012603 16.70, GG1024_02 15.95, GG012601 15.35</t>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>GG012603 16.70, GG1024_02 15.95, GG012601* 15.35</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr"/>
+      <c r="A29" s="7" t="inlineStr"/>
       <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
@@ -1669,21 +1921,31 @@
       <c r="F29" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>+0.39 / −1.40</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
         <v>12.6</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="6" t="n">
         <v>14.39</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>14.00% +0.39%/−1.40% (12.60% — 14.39%)</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>GG1024 13.34</t>
         </is>
@@ -1718,28 +1980,38 @@
       <c r="F30" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>±2.40</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n">
         <v>21.6</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="6" t="n">
         <v>26.4</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="J30" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>24.00% ±2.40% (21.60% — 26.40%)</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr"/>
+      <c r="A31" s="7" t="inlineStr"/>
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -1759,28 +2031,38 @@
       <c r="F31" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>+1.59 / −1.47</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>18.53</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>21.59</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>3.06</v>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>20.00% +1.59%/−1.47% (18.53% — 21.59%)</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>GP072501/1 21.36, GP082501/1 21.29, GP0824_01 20.79, GP072501/2 19.81</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr"/>
+      <c r="A32" s="7" t="inlineStr"/>
       <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
@@ -1800,28 +2082,38 @@
       <c r="F32" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>+0.52 / −1.80</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="6" t="n">
         <v>18.52</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="J32" s="6" t="n">
         <v>2.32</v>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +0.52%/−1.80% (16.20% — 18.52%)</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>GP052501 18.52</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr"/>
+      <c r="A33" s="7" t="inlineStr"/>
       <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
@@ -1841,21 +2133,31 @@
       <c r="F33" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>+0.19 / −1.60</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="6" t="n">
         <v>16.19</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="J33" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>16.00% +0.19%/−1.60% (14.40% — 16.19%)</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>GP082501/2 15.70</t>
         </is>
@@ -1890,28 +2192,38 @@
       <c r="F34" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>±1.20</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="6" t="n">
         <v>13.2</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="J34" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>12.00% ±1.20% (10.80% — 13.20%)</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>GRC102501/2 11.53</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr"/>
+      <c r="A35" s="7" t="inlineStr"/>
       <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
@@ -1931,21 +2243,31 @@
       <c r="F35" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>±0.70</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
         <v>6.3</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="6" t="n">
         <v>7.7</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="J35" s="6" t="n">
         <v>1.4</v>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>7.00% ±0.70% (6.30% — 7.70%)</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
         <is>
           <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>GRC102501/1 7.05</t>
         </is>
@@ -1980,28 +2302,38 @@
       <c r="F36" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>±2.20</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="J36" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr">
         <is>
           <t>HPA1024_01 21.61, HPA052501 20.39</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr"/>
+      <c r="A37" s="7" t="inlineStr"/>
       <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
@@ -2021,21 +2353,31 @@
       <c r="F37" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>+1.79 / −1.80</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="6" t="n">
         <v>19.79</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="J37" s="6" t="n">
         <v>3.59</v>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +1.79%/−1.80% (16.20% — 19.79%)</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K37" s="8" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>HPA1024 17.31</t>
         </is>
@@ -2070,28 +2412,38 @@
       <c r="F38" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>+2.00 / −1.99</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n">
         <v>18.01</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="J38" s="6" t="n">
         <v>3.99</v>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>20.00% +2.00%/−1.99% (18.01% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601 18.16</t>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601* 18.16</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr"/>
+      <c r="A39" s="7" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
@@ -2111,28 +2463,38 @@
       <c r="F39" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>+0.00 / −1.28</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="n">
         <v>16.72</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="J39" s="6" t="n">
         <v>1.28</v>
       </c>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +0.00%/−1.28% (16.72% — 18.00%)</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
         <is>
           <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
-      <c r="K39" s="8" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr"/>
+      <c r="A40" s="7" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
@@ -2152,174 +2514,206 @@
       <c r="F40" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>+0.71 / −1.60</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="6" t="n">
         <v>16.71</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="J40" s="6" t="n">
         <v>2.31</v>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>16.00% +0.71%/−1.60% (14.40% — 16.71%)</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K40" s="8" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>JD012603/01 16.71, JD012603/02V 15.16</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>JD_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_JD-IV</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>+0.39 / −1.40</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>14.00% +0.39%/−1.40% (12.60% — 14.39%)</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>JD112501* 13.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Jokerz 31</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>J31</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>J31_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_J31-I</t>
         </is>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F42" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>±2.20</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I42" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="J42" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>J31122501 21.84, J31112501 20.21</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr"/>
-      <c r="C42" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>J31_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_J31-II</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>J31102501 17.32</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Kush Crasher</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>KC_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_KC-I</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>+1.79 / −1.80</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H43" s="6" t="n">
-        <v>19.8</v>
-      </c>
       <c r="I43" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>KC102501 17.04</t>
+        <v>19.79</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +1.79%/−1.80% (16.20% — 19.79%)</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>J31102501 17.32</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -2329,791 +2723,971 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>MB_THC18 : CBD1</t>
+          <t>KC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-I</t>
+          <t>QCSP_001_KC-I</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>±1.80</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>KC102501 17.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>MB_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_MB-I</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>+1.80 / −1.17</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="n">
         <v>16.83</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I45" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="J45" s="6" t="n">
         <v>2.97</v>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +1.80%/−1.17% (16.83% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K44" s="8" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>MB0824_04 18.67</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr"/>
-      <c r="B45" s="5" t="inlineStr"/>
-      <c r="C45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>MB_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_MB-II</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F46" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>+0.82 / −1.60</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I46" s="6" t="n">
         <v>16.82</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="J46" s="6" t="n">
         <v>2.42</v>
       </c>
-      <c r="J45" s="9" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>16.00% +0.82%/−1.60% (14.40% — 16.82%)</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>MB0824_05 16.82</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>OPM</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>OPM_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_OPM-I</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F47" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>±2.20</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="I47" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="J47" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K46" s="8" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>OPM1024 20.03</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>OPM_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_OPM-II</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>16.56</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="K47" s="8" t="inlineStr">
-        <is>
-          <t>OPM1024_02 18.04</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr"/>
+      <c r="A48" s="7" t="inlineStr"/>
       <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-III</t>
+          <t>QCSP_001_OPM-II</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>14.4</v>
+        <v>18</v>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>+1.79 / −1.44</t>
+        </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>16.55</v>
+        <v>16.56</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
+        <v>19.79</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +1.79%/−1.44% (16.56% — 19.79%)</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K48" s="8" t="inlineStr">
-        <is>
-          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>OPM1024_02 18.04</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr"/>
+      <c r="A49" s="7" t="inlineStr"/>
       <c r="B49" s="5" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC14 : CBD1</t>
+          <t>OPM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-IV</t>
+          <t>QCSP_001_OPM-III</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>12.6</v>
+        <v>16</v>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>+0.55 / −1.60</t>
+        </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
+        <v>16.55</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>16.00% +0.55%/−1.60% (14.40% — 16.55%)</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr">
-        <is>
-          <t>OPM052501 14.16</t>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr"/>
+      <c r="A50" s="7" t="inlineStr"/>
       <c r="B50" s="5" t="inlineStr"/>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC12 : CBD1</t>
+          <t>OPM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-V</t>
+          <t>QCSP_001_OPM-IV</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>10.8</v>
+        <v>14</v>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>+0.39 / −1.40</t>
+        </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>12.59</v>
+        <v>12.6</v>
       </c>
       <c r="I50" s="6" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="J50" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>RESERVE (contiguity bridge)</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
-        <is>
-          <t>— reserve grade (no current batch)</t>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>14.00% +0.39%/−1.40% (12.60% — 14.39%)</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>OPM052501 14.16</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr"/>
+      <c r="A51" s="7" t="inlineStr"/>
       <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC10 : CBD1</t>
+          <t>OPM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-VI</t>
+          <t>QCSP_001_OPM-V</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>+0.59 / −1.20</t>
+        </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="I51" s="6" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="J51" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="K51" s="8" t="inlineStr">
-        <is>
-          <t>OPM092501 9.43</t>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>12.00% +0.59%/−1.20% (10.80% — 12.59%)</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>RESERVE (contiguity bridge)</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr"/>
+      <c r="A52" s="7" t="inlineStr"/>
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr">
         <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>OPM_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_OPM-VI</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>+0.79 / −1.00</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>10.00% +0.79%/−1.00% (9.00% — 10.79%)</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>OPM092501 9.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_OPM-VII</t>
         </is>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F53" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>±0.80</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="n">
         <v>7.2</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="I53" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="J53" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>OPM112501 8.00, OPM122501 7.91</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>PM_THC14 : CBD1</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_PM-I</t>
         </is>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F54" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G53" s="6" t="n">
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>±1.40</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="n">
         <v>12.6</v>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="I54" s="6" t="n">
         <v>15.4</v>
       </c>
-      <c r="I53" s="6" t="n">
+      <c r="J54" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>14.00% ±1.40% (12.60% — 15.40%)</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K53" s="8" t="inlineStr">
+      <c r="M54" s="7" t="inlineStr">
         <is>
           <t>PM112501 13.33</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr"/>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>PM_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_PM-II</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="K54" s="8" t="inlineStr">
-        <is>
-          <t>PM092501 12.25</t>
-        </is>
-      </c>
-    </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr"/>
+      <c r="A55" s="7" t="inlineStr"/>
       <c r="B55" s="5" t="inlineStr"/>
       <c r="C55" s="5" t="inlineStr">
         <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>PM_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_PM-II</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>+0.59 / −1.20</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>12.00% +0.59%/−1.20% (10.80% — 12.59%)</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>PM092501 12.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr"/>
+      <c r="B56" s="5" t="inlineStr"/>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
           <t>III</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>PM_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_PM-III</t>
         </is>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="F56" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G55" s="6" t="n">
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>+0.79 / −1.00</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="H55" s="6" t="n">
+      <c r="I56" s="6" t="n">
         <v>10.79</v>
       </c>
-      <c r="I55" s="6" t="n">
+      <c r="J56" s="6" t="n">
         <v>1.79</v>
       </c>
-      <c r="J55" s="9" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>10.00% +0.79%/−1.00% (9.00% — 10.79%)</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K55" s="8" t="inlineStr">
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>PM072501 10.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Pure Michigen</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>PUM</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>PUM_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_PUM-I</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>PUM102501 15.63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>PUM</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>PUM_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_PUM-I</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>±1.60</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+        </is>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>PUM102501 15.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>SCR</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>SCR_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_SCR-I</t>
         </is>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F58" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>±2.20</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H57" s="6" t="n">
+      <c r="I58" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I57" s="6" t="n">
+      <c r="J58" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J57" s="7" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
+        </is>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K57" s="8" t="inlineStr">
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>SCR022601 21.92</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr"/>
-      <c r="B58" s="5" t="inlineStr"/>
-      <c r="C58" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="5" t="inlineStr"/>
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_SCR-II</t>
         </is>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F59" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G58" s="6" t="n">
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>+1.79 / −1.80</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
         <v>16.2</v>
       </c>
-      <c r="H58" s="6" t="n">
+      <c r="I59" s="6" t="n">
         <v>19.79</v>
       </c>
-      <c r="I58" s="6" t="n">
+      <c r="J59" s="6" t="n">
         <v>3.59</v>
       </c>
-      <c r="J58" s="9" t="inlineStr">
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>18.00% +1.79%/−1.80% (16.20% — 19.79%)</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K58" s="8" t="inlineStr">
+      <c r="M59" s="7" t="inlineStr">
         <is>
           <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Sleepy Joy</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>SJ</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>SJ_THC12 : CBD1</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_SJ-I</t>
         </is>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F60" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G59" s="6" t="n">
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>+1.20 / −1.03</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="n">
         <v>10.97</v>
       </c>
-      <c r="H59" s="6" t="n">
+      <c r="I60" s="6" t="n">
         <v>13.2</v>
       </c>
-      <c r="I59" s="6" t="n">
+      <c r="J60" s="6" t="n">
         <v>2.23</v>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>12.00% +1.20%/−1.03% (10.97% — 13.20%)</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K59" s="8" t="inlineStr">
+      <c r="M60" s="7" t="inlineStr">
         <is>
           <t>SJ102501 11.20</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr"/>
-      <c r="B60" s="5" t="inlineStr"/>
-      <c r="C60" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr"/>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>SJ_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_SJ-II</t>
         </is>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F61" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G60" s="6" t="n">
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>+0.96 / −1.00</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="H60" s="6" t="n">
+      <c r="I61" s="6" t="n">
         <v>10.96</v>
       </c>
-      <c r="I60" s="6" t="n">
+      <c r="J61" s="6" t="n">
         <v>1.96</v>
       </c>
-      <c r="J60" s="9" t="inlineStr">
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>10.00% +0.96%/−1.00% (9.00% — 10.96%)</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="K60" s="8" t="inlineStr">
+      <c r="M61" s="7" t="inlineStr">
         <is>
           <t>SJ092501 10.96, SJ112501 9.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Wedding Cake</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>WED</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>WED_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_WED-I</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I61" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="K61" s="8" t="inlineStr">
-        <is>
-          <t>WED102501 22.05</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>WED</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3123,32 +3697,101 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>WC_THC22 : CBD1</t>
+          <t>WED_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_WC-I</t>
+          <t>QCSP_001_WED-I</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G62" s="6" t="n">
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>±2.20</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="H62" s="6" t="n">
+      <c r="I62" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="I62" s="6" t="n">
+      <c r="J62" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="J62" s="7" t="inlineStr">
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
+        </is>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="K62" s="8" t="inlineStr">
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>WED102501 22.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>WC_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_WC-I</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>±2.20</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
+        </is>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>WC072501 22.11, WC082501 21.67</t>
         </is>
@@ -3165,7 +3808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3221,12 +3864,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ACC102501</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Amnesia Core Cut</t>
         </is>
@@ -3236,7 +3879,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>ACC_THC12 : CBD1</t>
         </is>
@@ -3244,7 +3887,7 @@
       <c r="E2" s="6" t="n">
         <v>12.91</v>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>owner-declared value</t>
         </is>
@@ -3254,19 +3897,19 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>AB092501</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Apple and Banana</t>
         </is>
@@ -3276,7 +3919,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>AB_THC16 : CBD1</t>
         </is>
@@ -3284,7 +3927,7 @@
       <c r="E3" s="6" t="n">
         <v>16.93</v>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>PP CoA #037 / ППК26005, 21.01.2026, UKIM</t>
         </is>
@@ -3294,19 +3937,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>BG1024</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Blue Gelato</t>
         </is>
@@ -3316,7 +3959,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>BG_THC26 : CBD1</t>
         </is>
@@ -3324,7 +3967,7 @@
       <c r="E4" s="6" t="n">
         <v>26.14</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>197-1-К/26, 07.08.2026, FARM</t>
         </is>
@@ -3334,15 +3977,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>BSS1024</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Blue Sunset Sherbet</t>
         </is>
@@ -3352,7 +3995,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>BSS_THC24 : CBD1</t>
         </is>
@@ -3360,7 +4003,7 @@
       <c r="E5" s="6" t="n">
         <v>25.01</v>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>197-2-К/26, 07.08.2026, FARM</t>
         </is>
@@ -3370,15 +4013,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>BSS1024_01</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Blue Sunset Sherbet</t>
         </is>
@@ -3388,7 +4031,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>BSS_THC24 : CBD1</t>
         </is>
@@ -3396,7 +4039,7 @@
       <c r="E6" s="6" t="n">
         <v>23.42</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ППК25176, 10.07.2025, UKIM</t>
         </is>
@@ -3406,19 +4049,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Blue Sunset Sherbet</t>
         </is>
@@ -3428,7 +4071,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>BSS_THC20 : CBD1</t>
         </is>
@@ -3436,7 +4079,7 @@
       <c r="E7" s="6" t="n">
         <v>20.39</v>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>In-house GC cross-check NGP/QCG/SOP-024, 28.11.2025, PP</t>
         </is>
@@ -3446,15 +4089,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3464,7 +4107,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>CJ_THC24 : CBD1</t>
         </is>
@@ -3472,7 +4115,7 @@
       <c r="E8" s="6" t="n">
         <v>24.96</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>ППК26002, 21.01.2026, UKIM</t>
         </is>
@@ -3482,15 +4125,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CJ052501/01</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3500,7 +4143,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>CJ_THC24 : CBD1</t>
         </is>
@@ -3508,7 +4151,7 @@
       <c r="E9" s="6" t="n">
         <v>24.05</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>197-3-К/26, 07.08.2026, FARM</t>
         </is>
@@ -3518,15 +4161,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>CJ072501</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3536,7 +4179,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>CJ_THC24 : CBD1</t>
         </is>
@@ -3544,7 +4187,7 @@
       <c r="E10" s="6" t="n">
         <v>23.7</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>ППК25367, 28.11.2025, UKIM</t>
         </is>
@@ -3554,19 +4197,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>CJ1024</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3576,7 +4219,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>CJ_THC24 : CBD1</t>
         </is>
@@ -3584,7 +4227,7 @@
       <c r="E11" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>ППК25052, 26.02.2025, UKIM</t>
         </is>
@@ -3594,19 +4237,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>CJ092501</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3616,7 +4259,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>CJ_THC24 : CBD1</t>
         </is>
@@ -3624,7 +4267,7 @@
       <c r="E12" s="6" t="n">
         <v>22.3</v>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>ППК26007, 21.01.2026, UKIM</t>
         </is>
@@ -3634,15 +4277,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>CJ062501/1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3652,7 +4295,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>CJ_THC22 : CBD1</t>
         </is>
@@ -3660,7 +4303,7 @@
       <c r="E13" s="6" t="n">
         <v>21.51</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>ППК25321, 23.10.2025, UKIM</t>
         </is>
@@ -3670,15 +4313,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>CJ062501/2</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3688,7 +4331,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>CJ_THC20 : CBD1</t>
         </is>
@@ -3696,7 +4339,7 @@
       <c r="E14" s="6" t="n">
         <v>18.91</v>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>197-4-К/26, 07.08.2026, FARM</t>
         </is>
@@ -3706,19 +4349,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>CJ082501/2</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3728,7 +4371,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>CJ_THC20 : CBD1</t>
         </is>
@@ -3736,7 +4379,7 @@
       <c r="E15" s="6" t="n">
         <v>18.29</v>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>197-5-К/26, 07.08.2026, FARM</t>
         </is>
@@ -3746,15 +4389,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>CJ052501/02</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -3764,7 +4407,7 @@
           <t>VI</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>CJ_THC14 : CBD1</t>
         </is>
@@ -3772,7 +4415,7 @@
       <c r="E16" s="6" t="n">
         <v>14.93</v>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>ППК25281, 17.09.2025, UKIM</t>
         </is>
@@ -3782,19 +4425,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>CC012601/1</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Cash Cow</t>
         </is>
@@ -3804,7 +4447,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>CC_THC18 : CBD1</t>
         </is>
@@ -3812,7 +4455,7 @@
       <c r="E17" s="6" t="n">
         <v>17.67</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>197-6-К/26, 07.08.2026, FARM</t>
         </is>
@@ -3822,19 +4465,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>CC112501</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Cash Cow</t>
         </is>
@@ -3844,7 +4487,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>CC_THC14 : CBD1</t>
         </is>
@@ -3852,7 +4495,7 @@
       <c r="E18" s="6" t="n">
         <v>13.35</v>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>ППК26068, 11.05.2026, UKIM</t>
         </is>
@@ -3862,19 +4505,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>CC012603</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Cash Cow</t>
         </is>
@@ -3884,7 +4527,7 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>CC_THC12 : CBD1</t>
         </is>
@@ -3892,7 +4535,7 @@
       <c r="E19" s="6" t="n">
         <v>12.32</v>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>owner-declared value</t>
         </is>
@@ -3902,19 +4545,19 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>CF102501</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Chem Flyer</t>
         </is>
@@ -3924,7 +4567,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>CF_THC10 : CBD1</t>
         </is>
@@ -3932,7 +4575,7 @@
       <c r="E20" s="6" t="n">
         <v>9.83</v>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>owner-declared value</t>
         </is>
@@ -3942,19 +4585,19 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Clemosa a bud</t>
         </is>
@@ -3964,7 +4607,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>CLE_THC8 : CBD1</t>
         </is>
@@ -3972,7 +4615,7 @@
       <c r="E21" s="6" t="n">
         <v>8.02</v>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>PP CoA #027 / ППК25370, 21.01.2026, UKIM</t>
         </is>
@@ -3982,15 +4625,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>FB012603</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
@@ -4000,7 +4643,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>FB_THC20 : CBD1</t>
         </is>
@@ -4008,7 +4651,7 @@
       <c r="E22" s="6" t="n">
         <v>20.83</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>ППК26112, 30.06.2026, UKIM</t>
         </is>
@@ -4018,19 +4661,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>FB012602</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
@@ -4040,7 +4683,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>FB_THC18 : CBD1</t>
         </is>
@@ -4048,7 +4691,7 @@
       <c r="E23" s="6" t="n">
         <v>18.86</v>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>197-7-К/26, 07.08.2026, FARM</t>
         </is>
@@ -4058,15 +4701,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>FB012603V</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
@@ -4076,7 +4719,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>FB_THC18 : CBD1</t>
         </is>
@@ -4084,7 +4727,7 @@
       <c r="E24" s="6" t="n">
         <v>18.29</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>ППК26110, 30.06.2026, UKIM</t>
         </is>
@@ -4094,19 +4737,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>FB112501</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
@@ -4116,7 +4759,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>FB_THC18 : CBD1</t>
         </is>
@@ -4124,7 +4767,7 @@
       <c r="E25" s="6" t="n">
         <v>16.69</v>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>ППК26066, 11.05.2026, UKIM</t>
         </is>
@@ -4134,19 +4777,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>FB012601/1</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
@@ -4156,7 +4799,7 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>FB_THC14 : CBD1</t>
         </is>
@@ -4164,7 +4807,7 @@
       <c r="E26" s="6" t="n">
         <v>14.68</v>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>ППК26067, 11.05.2026, UKIM</t>
         </is>
@@ -4174,15 +4817,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>FB032601</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
@@ -4192,7 +4835,7 @@
           <t>V</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>FB_THC12 : CBD1</t>
         </is>
@@ -4200,7 +4843,7 @@
       <c r="E27" s="6" t="n">
         <v>12.39</v>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>ППК26127, 21.07.2026, UKIM</t>
         </is>
@@ -4210,19 +4853,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>GG032601</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
@@ -4232,7 +4875,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>GG_THC18 : CBD1</t>
         </is>
@@ -4240,7 +4883,7 @@
       <c r="E28" s="6" t="n">
         <v>18.98</v>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>ППК26128, 21.07.2026, UKIM</t>
         </is>
@@ -4250,19 +4893,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>GG1024_01</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
@@ -4272,7 +4915,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>GG_THC18 : CBD1</t>
         </is>
@@ -4280,7 +4923,7 @@
       <c r="E29" s="6" t="n">
         <v>18.67</v>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>197-9-К/26, 07.08.2026, FARM</t>
         </is>
@@ -4290,15 +4933,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>GG112501</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
@@ -4308,7 +4951,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>GG_THC18 : CBD1</t>
         </is>
@@ -4316,7 +4959,7 @@
       <c r="E30" s="6" t="n">
         <v>17.94</v>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>ППК26061, 11.05.2026, UKIM</t>
         </is>
@@ -4326,19 +4969,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>GG012603</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
@@ -4348,7 +4991,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>GG_THC16 : CBD1</t>
         </is>
@@ -4356,7 +4999,7 @@
       <c r="E31" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>197-8-К/26, 07.08.2026, FARM</t>
         </is>
@@ -4366,15 +5009,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>GG1024_02</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
@@ -4384,7 +5027,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>GG_THC16 : CBD1</t>
         </is>
@@ -4392,7 +5035,7 @@
       <c r="E32" s="6" t="n">
         <v>15.95</v>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>ППК25140, 22.05.2025, UKIM</t>
         </is>
@@ -4402,19 +5045,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>GG012601</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>GG012601*</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
@@ -4424,7 +5067,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>GG_THC16 : CBD1</t>
         </is>
@@ -4432,7 +5075,7 @@
       <c r="E33" s="6" t="n">
         <v>15.35</v>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>ППК26062, 11.05.2026, UKIM</t>
         </is>
@@ -4442,19 +5085,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>GG1024</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
@@ -4464,7 +5107,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>GG_THC14 : CBD1</t>
         </is>
@@ -4472,7 +5115,7 @@
       <c r="E34" s="6" t="n">
         <v>13.34</v>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed), 23.04.2025, UKIM</t>
         </is>
@@ -4482,15 +5125,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>P160012</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4500,7 +5143,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
@@ -4508,7 +5151,7 @@
       <c r="E35" s="6" t="n">
         <v>26.32</v>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>ППК26117, 06.07.2026, UKIM</t>
         </is>
@@ -4518,19 +5161,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>GP092501</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4540,7 +5183,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
@@ -4548,7 +5191,7 @@
       <c r="E36" s="6" t="n">
         <v>25.73</v>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>ППК26009, 21.01.2026, UKIM</t>
         </is>
@@ -4558,15 +5201,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>P160022</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4576,7 +5219,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
@@ -4584,7 +5227,7 @@
       <c r="E37" s="6" t="n">
         <v>25.72</v>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>ППК26118, 06.07.2026, UKIM</t>
         </is>
@@ -4594,19 +5237,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4616,7 +5259,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
@@ -4624,7 +5267,7 @@
       <c r="E38" s="6" t="n">
         <v>25.45</v>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>ППК25175, 10.07.2025, UKIM</t>
         </is>
@@ -4634,15 +5277,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>GP062501</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4652,7 +5295,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
@@ -4660,7 +5303,7 @@
       <c r="E39" s="6" t="n">
         <v>24.89</v>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024, 28.11.2025, PP</t>
         </is>
@@ -4670,19 +5313,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>P160032</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4692,7 +5335,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
@@ -4700,7 +5343,7 @@
       <c r="E40" s="6" t="n">
         <v>24.78</v>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>ППК26119, 06.07.2026, UKIM</t>
         </is>
@@ -4710,19 +5353,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>GP0824_02</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4732,7 +5375,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
@@ -4740,7 +5383,7 @@
       <c r="E41" s="6" t="n">
         <v>22.61</v>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>197-11-К/26, 07.08.2026, FARM</t>
         </is>
@@ -4750,15 +5393,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>GP072501/1</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4768,7 +5411,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>GP_THC20 : CBD1</t>
         </is>
@@ -4776,7 +5419,7 @@
       <c r="E42" s="6" t="n">
         <v>21.36</v>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>PP CoA #018 / ППК25378, 21.01.2026, UKIM</t>
         </is>
@@ -4786,19 +5429,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4808,7 +5451,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>GP_THC20 : CBD1</t>
         </is>
@@ -4816,7 +5459,7 @@
       <c r="E43" s="6" t="n">
         <v>21.29</v>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>PP CoA #020 / ППК25380, 21.01.2026, UKIM</t>
         </is>
@@ -4826,15 +5469,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>GP0824_01</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4844,7 +5487,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>GP_THC20 : CBD1</t>
         </is>
@@ -4852,7 +5495,7 @@
       <c r="E44" s="6" t="n">
         <v>20.79</v>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>ППК25105, 17.04.2025, UKIM</t>
         </is>
@@ -4862,19 +5505,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4884,7 +5527,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>GP_THC20 : CBD1</t>
         </is>
@@ -4892,7 +5535,7 @@
       <c r="E45" s="6" t="n">
         <v>19.81</v>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>PP CoA #019 / ППК25379, 21.01.2026, UKIM</t>
         </is>
@@ -4902,15 +5545,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>GP052501</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4920,7 +5563,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>GP_THC18 : CBD1</t>
         </is>
@@ -4928,7 +5571,7 @@
       <c r="E46" s="6" t="n">
         <v>18.52</v>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>197-10-К/26, 07.08.2026, FARM</t>
         </is>
@@ -4938,15 +5581,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>GP082501/2</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -4956,7 +5599,7 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>GP_THC16 : CBD1</t>
         </is>
@@ -4964,7 +5607,7 @@
       <c r="E47" s="6" t="n">
         <v>15.7</v>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>197-12-К/26, 07.08.2026, FARM</t>
         </is>
@@ -4974,15 +5617,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>GRC102501/2</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Graps &amp; Creme</t>
         </is>
@@ -4992,7 +5635,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>GRC_THC12 : CBD1</t>
         </is>
@@ -5000,7 +5643,7 @@
       <c r="E48" s="6" t="n">
         <v>11.53</v>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>051-6-K/26, 04.03.2026, FARM</t>
         </is>
@@ -5010,15 +5653,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>GRC102501/1</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Graps &amp; Creme</t>
         </is>
@@ -5028,7 +5671,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>GRC_THC7 : CBD1</t>
         </is>
@@ -5036,7 +5679,7 @@
       <c r="E49" s="6" t="n">
         <v>7.05</v>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>owner-declared value</t>
         </is>
@@ -5046,19 +5689,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>HPA1024_01</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>High Pro Amnesia</t>
         </is>
@@ -5068,7 +5711,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>HPA_THC22 : CBD1</t>
         </is>
@@ -5076,7 +5719,7 @@
       <c r="E50" s="6" t="n">
         <v>21.61</v>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>197-14-К/26, 07.08.2026, FARM</t>
         </is>
@@ -5086,15 +5729,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>High Pro Amnesia</t>
         </is>
@@ -5104,7 +5747,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>HPA_THC22 : CBD1</t>
         </is>
@@ -5112,7 +5755,7 @@
       <c r="E51" s="6" t="n">
         <v>20.39</v>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>ППК25278, 19.09.2025, UKIM</t>
         </is>
@@ -5122,15 +5765,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>HPA1024</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>High Pro Amnesia</t>
         </is>
@@ -5140,7 +5783,7 @@
           <t>II</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>HPA_THC18 : CBD1</t>
         </is>
@@ -5148,7 +5791,7 @@
       <c r="E52" s="6" t="n">
         <v>17.31</v>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>197-13-К/26, 07.08.2026, FARM</t>
         </is>
@@ -5158,15 +5801,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>JD012603/02</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
@@ -5176,7 +5819,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>JD_THC20 : CBD1</t>
         </is>
@@ -5184,7 +5827,7 @@
       <c r="E53" s="6" t="n">
         <v>20.54</v>
       </c>
-      <c r="F53" s="8" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>ППК26113, 30.06.2026, UKIM</t>
         </is>
@@ -5194,15 +5837,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>JD112501</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
@@ -5212,7 +5855,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>JD_THC20 : CBD1</t>
         </is>
@@ -5220,7 +5863,7 @@
       <c r="E54" s="6" t="n">
         <v>20.32</v>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>197-15-К/26, 07.08.2026, FARM</t>
         </is>
@@ -5230,15 +5873,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>JD022601</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
@@ -5248,7 +5891,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>JD_THC20 : CBD1</t>
         </is>
@@ -5256,7 +5899,7 @@
       <c r="E55" s="6" t="n">
         <v>18.58</v>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>ППК26115, 30.06.2026, UKIM</t>
         </is>
@@ -5266,19 +5909,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>JD012601</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>JD012601*</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
@@ -5288,7 +5931,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>JD_THC20 : CBD1</t>
         </is>
@@ -5296,7 +5939,7 @@
       <c r="E56" s="6" t="n">
         <v>18.16</v>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>ППК26064, 11.05.2026, UKIM</t>
         </is>
@@ -5306,19 +5949,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>JD012603/01</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
@@ -5328,7 +5971,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>JD_THC16 : CBD1</t>
         </is>
@@ -5336,7 +5979,7 @@
       <c r="E57" s="6" t="n">
         <v>16.71</v>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>owner-declared value</t>
         </is>
@@ -5346,19 +5989,19 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>JD012603/02V</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
@@ -5368,7 +6011,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>JD_THC16 : CBD1</t>
         </is>
@@ -5376,7 +6019,7 @@
       <c r="E58" s="6" t="n">
         <v>15.16</v>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>ППК26111, 30.06.2026, UKIM</t>
         </is>
@@ -5386,1071 +6029,1111 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>JD112501*</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>JD_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>ППК26065, 11.05.2026, UKIM</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>J31122501</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Jokerz 31</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>J31_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E60" s="6" t="n">
         <v>21.84</v>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>machine-trimmed preparation, CoQ-forming (CoQ-PP-2026-0054); hand-trimmed 19.84 is the experimental prep</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>J31112501</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Jokerz 31</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>J31_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E61" s="6" t="n">
         <v>20.21</v>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>100-1-K/26, 09.04.2026, FARM</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>J31102501</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Jokerz 31</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>J31_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E62" s="6" t="n">
         <v>17.32</v>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>197-16-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>KC102501</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Kush Crasher</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>KC_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E63" s="6" t="n">
         <v>17.04</v>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>051-4-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>MB0824_04</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Motor Breath</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>MB_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E64" s="6" t="n">
         <v>18.67</v>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>ППК25118, 06.05.2025, UKIM</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Motor Breath</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>MB_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E65" s="6" t="n">
         <v>16.82</v>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>ППК52211, 28.07.2025, UKIM</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>OPM1024</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>OPM_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E66" s="6" t="n">
         <v>20.03</v>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>197-17-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>OPM1024_02</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E67" s="6" t="n">
         <v>18.04</v>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>197-18-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>III</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>OPM_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E68" s="6" t="n">
         <v>16.55</v>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>ППК25210, 28.07.2025, UKIM</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>OMP1024_01</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>III</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>OPM_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E69" s="6" t="n">
         <v>15.38</v>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>ППК25117, 06.05.2025, UKIM</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>OPM052501</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>OPM_THC14 : CBD1</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E70" s="6" t="n">
         <v>14.16</v>
       </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>ППК52557, 05.09.2025, UKIM</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>OPM_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E71" s="6" t="n">
         <v>9.43</v>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>ППК26008, 21.01.2026, UKIM</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>OPM112501</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E72" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>ППК26031, 05.03.2026, UKIM</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>OPM122501</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E73" s="6" t="n">
         <v>7.91</v>
       </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>197-19-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>PM112501</t>
         </is>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="C73" s="11" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>PM_THC14 : CBD1</t>
         </is>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="E74" s="12" t="n">
         <v>13.33</v>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>ППК26030, 05.03.2026, UKIM</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G74" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>owner code THC12 infeasible for audited 13.33 — moved to THC14</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>PM092501</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>PM_THC12 : CBD1</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E75" s="6" t="n">
         <v>12.25</v>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>197-20-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>PM072501</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>III</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>PM_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E76" s="6" t="n">
         <v>10.01</v>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>ППК25368, 28.11.2025, UKIM</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="H76" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>PUM102501</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Pure Michigen</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>PUM_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E77" s="6" t="n">
         <v>15.63</v>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>owner-declared value</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>SCR022601</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>SCR_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E78" s="6" t="n">
         <v>21.92</v>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>ППК26116, 06.07.2026, UKIM</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="H78" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>SCR012601</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E79" s="6" t="n">
         <v>18.07</v>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>owner-declared value</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>SCR012603</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E80" s="6" t="n">
         <v>17.84</v>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>197-21-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="H80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>SCR112501</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E81" s="6" t="n">
         <v>17.13</v>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>ППК26069, 11.05.2026, UKIM</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>SJ102501</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>Sleepy Joy</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>SJ_THC12 : CBD1</t>
         </is>
       </c>
-      <c r="E81" s="6" t="n">
+      <c r="E82" s="6" t="n">
         <v>11.2</v>
       </c>
-      <c r="F81" s="8" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>051-3-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="H82" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>SJ092501</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>Sleepy Joy</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>SJ_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E83" s="6" t="n">
         <v>10.96</v>
       </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>ППК26006, 21.01.2026, UKIM</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="H83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>SJ112501</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>Sleepy Joy</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>SJ_THC10 : CBD1</t>
         </is>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="E84" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>051-2-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="H84" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>WED102501</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>Wedding Cake</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>WED_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E85" s="6" t="n">
         <v>22.05</v>
       </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>owner-declared value</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="H85" s="7" t="inlineStr">
         <is>
           <t>declared value — no eCoA yet, grade provisional until tested</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>WC072501</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>Wedding Crasher</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>WC_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E86" s="6" t="n">
         <v>22.11</v>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>ППК25369, 28.11.2025, UKIM</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr">
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>WC082501</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>Wedding Crasher</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>WC_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E87" s="6" t="n">
         <v>21.67</v>
       </c>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>ППК26001, 21.01.2026, UKIM</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6463,7 +7146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6714,6 +7397,30 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>Truth-check finding (27.08.2026): certificate ППК26065 (13.93, CNP, 11.05.2026) prints серија JD112501* — the milled Jelly Donutz presentation, a separate register batch — and was misattributed to JD112501 (whole flower, retest 20.32) in the source dataset. Reattributed; JD112501* now carries its own grade JD_THC14:CBD1 (12.60 — 14.39).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Grades whose upper bound is pinned by the grade above print +0.00% up-tolerance (CJ-II, CJ-III, CJ-IV): the nominal sits at the very top of its window — the mathematically forced consequence of the strongest-first maximum-range rule with even nominals two steps apart. Management may instead grant each such grade a small up-headroom at the cost of the grade above; flag for decision if the +0.00 display is unacceptable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>Batches on declared values (no eCoA yet): ACC102501, CC012603, CF102501, JD012603/01, PUM102501 (T2 re-analysis sampled 12.08.2026, results pending), SCR012601, WED102501, JD022601, GRC102501/1, P160012, P160022, P160032 — their grades are provisional.</t>
         </is>
       </c>

--- a/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
+++ b/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rules: nominal = whole even number; range &lt;= 10% of nominal each side; two-decimal bounds; no overlap within a strain; strongest grade takes the maximum range first; every batch falls in exactly one grade.</t>
+          <t>Rules: nominal = whole even number (adjacent odd only where symmetry is impossible); tolerance EQUAL above and below the nominal, at most 10% of it; two-decimal bounds; no overlap; contiguous ladders; strongest grade takes the maximum range first; every batch falls in exactly one grade.</t>
         </is>
       </c>
     </row>
@@ -855,21 +855,21 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>+1.59 / −2.00</t>
+          <t>±1.59</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18</v>
+        <v>18.41</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>21.59</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>3.59</v>
+        <v>3.18</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>20.00% +1.59%/−2.00% (18.00% — 21.59%)</t>
+          <t>20.00% ±1.59% (18.41% — 21.59%)</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -914,26 +914,26 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>+2.40 / −1.99</t>
+          <t>±2.40</t>
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>22.01</v>
+        <v>21.6</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>26.4</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>4.39</v>
+        <v>4.8</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>24.00% +2.40%/−1.99% (22.01% — 26.40%)</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>24.00% ±2.40% (21.60% — 26.40%)</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC22 : CBD1</t>
+          <t>CJ_THC21 : CBD1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -961,30 +961,30 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>+0.00 / −1.99</t>
+          <t>±0.59</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>20.01</v>
+        <v>20.41</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>22</v>
+        <v>21.59</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>1.99</v>
+        <v>1.18</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>22.00% +0.00%/−1.99% (20.01% — 22.00%)</t>
+          <t>21.00% ±0.59% (20.41% — 21.59%)</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC20 : CBD1</t>
+          <t>CJ_THC19 : CBD1</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1012,30 +1012,30 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>+0.00 / −1.99</t>
+          <t>±1.40</t>
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>18.01</v>
+        <v>17.6</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>1.99</v>
+        <v>2.8</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>20.00% +0.00%/−1.99% (18.01% — 20.00%)</t>
+          <t>19.00% ±1.40% (17.60% — 20.40%)</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC18 : CBD1</t>
+          <t>CJ_THC17 : CBD1</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1063,30 +1063,30 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>+0.00 / −1.80</t>
+          <t>±0.59</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>16.2</v>
+        <v>16.41</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>18</v>
+        <v>17.59</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>18.00% +0.00%/−1.80% (16.20% — 18.00%)</t>
+          <t>17.00% ±0.59% (16.41% — 17.59%)</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>RESERVE (contiguity bridge)</t>
+          <t>RESERVE (contiguity bridge) — ODD nominal (fallback rule 5)</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC16 : CBD1</t>
+          <t>CJ_THC15 : CBD1</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1114,145 +1114,145 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>±1.40</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>15.00% ±1.40% (13.60% — 16.40%)</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>CJ052501/02 14.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CC_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CC-I</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>±1.40</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.40% (16.60% — 19.40%)</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>CC012601/1 17.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>CC_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CC-II</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>+0.19 / −1.06</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>16.19</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>16.00% +0.19%/−1.06% (14.94% — 16.19%)</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>±0.59</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>16.00% ±0.59% (15.41% — 16.59%)</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>— reserve grade (no current batch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>CJ_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CJ-VI</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>+0.93 / −1.40</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>14.00% +0.93%/−1.40% (12.60% — 14.93%)</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>CJ052501/02 14.93</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Cash Cow</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>CC_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC-I</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>±1.80</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>CC012601/1 17.67</t>
         </is>
       </c>
     </row>
@@ -1261,49 +1261,49 @@
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>CC_THC16 : CBD1</t>
+          <t>CC_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CC-II</t>
+          <t>QCSP_001_CC-III</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>+0.19 / −1.60</t>
+          <t>±1.40</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>14.4</v>
+        <v>12.6</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>16.19</v>
+        <v>15.4</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>16.00% +0.19%/−1.60% (14.40% — 16.19%)</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>RESERVE (contiguity bridge)</t>
+          <t>14.00% ±1.40% (12.60% — 15.40%)</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>— reserve grade (no current batch)</t>
+          <t>CC112501 13.35</t>
         </is>
       </c>
     </row>
@@ -1312,39 +1312,39 @@
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>CC_THC14 : CBD1</t>
+          <t>CC_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CC-III</t>
+          <t>QCSP_001_CC-IV</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>+0.39 / −1.40</t>
+          <t>±0.59</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>12.6</v>
+        <v>11.41</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>14.39</v>
+        <v>12.59</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>14.00% +0.39%/−1.40% (12.60% — 14.39%)</t>
+          <t>12.00% ±0.59% (11.41% — 12.59%)</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -1354,70 +1354,78 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>CC112501 13.35</t>
+          <t>CC012603 12.32</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>CC_THC12 : CBD1</t>
+          <t>CF_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CC-IV</t>
+          <t>QCSP_001_CF-I</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>+0.59 / −1.20</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>12.59</v>
+        <v>11</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>12.00% +0.59%/−1.20% (10.80% — 12.59%)</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>CC012603 12.32</t>
+          <t>CF102501 9.83</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Clemosa a bud</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1427,34 +1435,34 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>CF_THC10 : CBD1</t>
+          <t>CLE_THC8 : CBD1</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CF-I</t>
+          <t>QCSP_001_CLE-I</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>±1.00</t>
+          <t>±0.80</t>
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -1464,19 +1472,19 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>CF102501 9.83</t>
+          <t>CLE072501 8.02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1486,93 +1494,85 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>CLE_THC8 : CBD1</t>
+          <t>FB_THC21 : CBD1</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CLE-I</t>
+          <t>QCSP_001_FB-I</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>±0.80</t>
+          <t>±1.68</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>7.2</v>
+        <v>19.32</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>22.68</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.6</v>
+        <v>3.36</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>21.00% ±1.68% (19.32% — 22.68%)</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>CLE072501 8.02</t>
+          <t>FB012603 20.83</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>FB</t>
-        </is>
-      </c>
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>FB_THC20 : CBD1</t>
+          <t>FB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-I</t>
+          <t>QCSP_001_FB-II</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>+2.00 / −1.13</t>
+          <t>±1.31</t>
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>18.87</v>
+        <v>16.69</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>22</v>
+        <v>19.31</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>3.13</v>
+        <v>2.62</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>20.00% +2.00%/−1.13% (18.87% — 22.00%)</t>
+          <t>18.00% ±1.31% (16.69% — 19.31%)</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>FB012603 20.83</t>
+          <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
         </is>
       </c>
     </row>
@@ -1591,49 +1591,49 @@
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>FB_THC18 : CBD1</t>
+          <t>FB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-II</t>
+          <t>QCSP_001_FB-III</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>+0.86 / −1.80</t>
+          <t>±0.68</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>16.2</v>
+        <v>15.32</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>18.86</v>
+        <v>16.68</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>2.66</v>
+        <v>1.36</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>18.00% +0.86%/−1.80% (16.20% — 18.86%)</t>
+          <t>16.00% ±0.68% (15.32% — 16.68%)</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
@@ -1642,49 +1642,49 @@
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>FB_THC16 : CBD1</t>
+          <t>FB_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-III</t>
+          <t>QCSP_001_FB-IV</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>+0.19 / −1.31</t>
+          <t>±1.31</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
-        <v>14.69</v>
+        <v>12.69</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>16.19</v>
+        <v>15.31</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.5</v>
+        <v>2.62</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>16.00% +0.19%/−1.31% (14.69% — 16.19%)</t>
+          <t>14.00% ±1.31% (12.69% — 15.31%)</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>RESERVE (contiguity bridge)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>— reserve grade (no current batch)</t>
+          <t>FB012601/1 14.68</t>
         </is>
       </c>
     </row>
@@ -1693,39 +1693,39 @@
       <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>FB_THC14 : CBD1</t>
+          <t>FB_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-IV</t>
+          <t>QCSP_001_FB-V</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>+0.68 / −1.40</t>
+          <t>±0.68</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>12.6</v>
+        <v>11.32</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>14.68</v>
+        <v>12.68</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>14.00% +0.68%/−1.40% (12.60% — 14.68%)</t>
+          <t>12.00% ±0.68% (11.32% — 12.68%)</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -1735,48 +1735,56 @@
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>FB012601/1 14.68</t>
+          <t>FB032601 12.39</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr"/>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>FB_THC12 : CBD1</t>
+          <t>GG_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-V</t>
+          <t>QCSP_001_GG-I</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>+0.59 / −1.20</t>
+          <t>±1.29</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>10.8</v>
+        <v>16.71</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>12.59</v>
+        <v>19.29</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>1.79</v>
+        <v>2.58</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>12.00% +0.59%/−1.20% (10.80% — 12.59%)</t>
+          <t>18.00% ±1.29% (16.71% — 19.29%)</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -1786,56 +1794,48 @@
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>FB032601 12.39</t>
+          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>GG</t>
-        </is>
-      </c>
+      <c r="A27" s="7" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>GG_THC18 : CBD1</t>
+          <t>GG_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-I</t>
+          <t>QCSP_001_GG-II</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>+1.80 / −1.29</t>
+          <t>±0.70</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>16.71</v>
+        <v>15.3</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>19.8</v>
+        <v>16.7</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.09</v>
+        <v>1.4</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>18.00% +1.80%/−1.29% (16.71% — 19.80%)</t>
+          <t>16.00% ±0.70% (15.30% — 16.70%)</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
+          <t>GG012603 16.70, GG1024_02 15.95, GG012601* 15.35</t>
         </is>
       </c>
     </row>
@@ -1854,159 +1854,159 @@
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>GG_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_GG-III</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>±1.29</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>14.00% ±1.29% (12.71% — 15.29%)</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>GG1024 13.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>GP_THC25 : CBD1</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_GP-I</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>±2.47</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>25.00% ±2.47% (22.53% — 27.47%)</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>GG_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GG-II</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>+0.70 / −1.60</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>16.00% +0.70%/−1.60% (14.40% — 16.70%)</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>GG012603 16.70, GG1024_02 15.95, GG012601* 15.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>GG_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GG-III</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>+0.39 / −1.40</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>14.00% +0.39%/−1.40% (12.60% — 14.39%)</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>GG1024 13.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>GP</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-I</t>
+          <t>QCSP_001_GP-II</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>±2.40</t>
+          <t>±0.52</t>
         </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>21.6</v>
+        <v>21.48</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>26.4</v>
+        <v>22.52</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>24.00% ±2.40% (21.60% — 26.40%)</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>22.00% ±0.52% (21.48% — 22.52%)</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-II</t>
+          <t>QCSP_001_GP-III</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
@@ -2033,21 +2033,21 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>+1.59 / −1.47</t>
+          <t>±1.47</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
         <v>18.53</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>21.59</v>
+        <v>21.47</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>20.00% +1.59%/−1.47% (18.53% — 21.59%)</t>
+          <t>20.00% ±1.47% (18.53% — 21.47%)</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
@@ -2066,7 +2066,7 @@
       <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-III</t>
+          <t>QCSP_001_GP-IV</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
@@ -2084,21 +2084,21 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>+0.52 / −1.80</t>
+          <t>±0.52</t>
         </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>16.2</v>
+        <v>17.48</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>18.52</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>18.00% +0.52%/−1.80% (16.20% — 18.52%)</t>
+          <t>18.00% ±0.52% (17.48% — 18.52%)</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
@@ -2117,7 +2117,7 @@
       <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-IV</t>
+          <t>QCSP_001_GP-V</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -2135,21 +2135,21 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>+0.19 / −1.60</t>
+          <t>±1.47</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>14.4</v>
+        <v>14.53</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>16.19</v>
+        <v>17.47</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>1.79</v>
+        <v>2.94</v>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>16.00% +0.19%/−1.60% (14.40% — 16.19%)</t>
+          <t>16.00% ±1.47% (14.53% — 17.47%)</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
@@ -2355,21 +2355,21 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>+1.79 / −1.80</t>
+          <t>±1.79</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>16.2</v>
+        <v>16.21</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>19.79</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>18.00% +1.79%/−1.80% (16.20% — 19.79%)</t>
+          <t>18.00% ±1.79% (16.21% — 19.79%)</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>JD_THC20 : CBD1</t>
+          <t>JD_THC19 : CBD1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2410,30 +2410,30 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>+2.00 / −1.99</t>
+          <t>±1.90</t>
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>18.01</v>
+        <v>17.1</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3.99</v>
+        <v>3.8</v>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>20.00% +2.00%/−1.99% (18.01% — 22.00%)</t>
-        </is>
-      </c>
-      <c r="L38" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>19.00% ±1.90% (17.10% — 20.90%)</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>JD_THC18 : CBD1</t>
+          <t>JD_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2461,35 +2461,35 @@
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>+0.00 / −1.28</t>
+          <t>±1.09</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>16.72</v>
+        <v>14.91</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>18</v>
+        <v>17.09</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>18.00% +0.00%/−1.28% (16.72% — 18.00%)</t>
+          <t>16.00% ±1.09% (14.91% — 17.09%)</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>RESERVE (contiguity bridge)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>— reserve grade (no current batch)</t>
+          <t>JD012603/01 16.71, JD012603/02V 15.16</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>JD_THC16 : CBD1</t>
+          <t>JD_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2512,25 +2512,25 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>+0.71 / −1.60</t>
+          <t>±0.90</t>
         </is>
       </c>
       <c r="H40" s="6" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>16.71</v>
+        <v>14.9</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>16.00% +0.71%/−1.60% (14.40% — 16.71%)</t>
+          <t>14.00% ±0.90% (13.10% — 14.90%)</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -2540,136 +2540,144 @@
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>JD012603/01 16.71, JD012603/02V 15.16</t>
+          <t>JD112501* 13.93</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr"/>
-      <c r="B41" s="5" t="inlineStr"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>J31</t>
+        </is>
+      </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>JD_THC14 : CBD1</t>
+          <t>J31_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-IV</t>
+          <t>QCSP_001_J31-I</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>+0.39 / −1.40</t>
+          <t>±2.20</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>12.6</v>
+        <v>19.8</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>14.39</v>
+        <v>24.2</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.79</v>
+        <v>4.4</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>14.00% +0.39%/−1.40% (12.60% — 14.39%)</t>
-        </is>
-      </c>
-      <c r="L41" s="9" t="inlineStr">
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>J31122501 21.84, J31112501 20.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>J31_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_J31-II</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>±1.79</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.79% (16.21% — 19.79%)</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr">
-        <is>
-          <t>JD112501* 13.93</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>J31</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>J31102501 17.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>J31_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_J31-I</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>±2.20</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="inlineStr">
-        <is>
-          <t>J31122501 21.84, J31112501 20.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr"/>
-      <c r="B43" s="5" t="inlineStr"/>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>J31_THC18 : CBD1</t>
+          <t>KC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_J31-II</t>
+          <t>QCSP_001_KC-I</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -2677,43 +2685,43 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>+1.79 / −1.80</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
         <v>16.2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>18.00% +1.79%/−1.80% (16.20% — 19.79%)</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>J31102501 17.32</t>
+          <t>KC102501 17.04</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -2723,12 +2731,12 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>KC_THC18 : CBD1</t>
+          <t>MB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_KC-I</t>
+          <t>QCSP_001_MB-I</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -2736,200 +2744,192 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>±1.80</t>
+          <t>±1.17</t>
         </is>
       </c>
       <c r="H44" s="6" t="n">
-        <v>16.2</v>
+        <v>16.83</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>19.8</v>
+        <v>19.17</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>3.6</v>
+        <v>2.34</v>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>18.00% ±1.17% (16.83% — 19.17%)</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>KC102501 17.04</t>
+          <t>MB0824_04 18.67</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Motor Breath</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
+      <c r="A45" s="7" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>MB_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_MB-II</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>±0.82</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>16.00% ±0.82% (15.18% — 16.82%)</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>MB0824_05 16.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>MB_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_MB-I</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>OPM_THC21 : CBD1</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_OPM-I</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>±2.10</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>21.00% ±2.10% (18.90% — 23.10%)</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>OPM1024 20.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr"/>
+      <c r="B47" s="5" t="inlineStr"/>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>OPM_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_OPM-II</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>+1.80 / −1.17</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>18.00% +1.80%/−1.17% (16.83% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>±0.89</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±0.89% (17.11% — 18.89%)</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>MB0824_04 18.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr"/>
-      <c r="B46" s="5" t="inlineStr"/>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>MB_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_MB-II</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>+0.82 / −1.60</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>16.00% +0.82%/−1.60% (14.40% — 16.82%)</t>
-        </is>
-      </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>MB0824_05 16.82</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>OPM</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>OPM_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_OPM-I</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>±2.20</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>OPM1024 20.03</t>
+          <t>OPM1024_02 18.04</t>
         </is>
       </c>
     </row>
@@ -2938,39 +2938,39 @@
       <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC18 : CBD1</t>
+          <t>OPM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-II</t>
+          <t>QCSP_001_OPM-III</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>+1.79 / −1.44</t>
+          <t>±1.10</t>
         </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>16.56</v>
+        <v>14.9</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>19.79</v>
+        <v>17.1</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>3.23</v>
+        <v>2.2</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>18.00% +1.79%/−1.44% (16.56% — 19.79%)</t>
+          <t>16.00% ±1.10% (14.90% — 17.10%)</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>OPM1024_02 18.04</t>
+          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
         </is>
       </c>
     </row>
@@ -2989,39 +2989,39 @@
       <c r="B49" s="5" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>OPM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-III</t>
+          <t>QCSP_001_OPM-IV</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>+0.55 / −1.60</t>
+          <t>±0.89</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>14.4</v>
+        <v>13.11</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>16.55</v>
+        <v>14.89</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>16.00% +0.55%/−1.60% (14.40% — 16.55%)</t>
+          <t>14.00% ±0.89% (13.11% — 14.89%)</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
+          <t>OPM052501 14.16</t>
         </is>
       </c>
     </row>
@@ -3040,49 +3040,49 @@
       <c r="B50" s="5" t="inlineStr"/>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC14 : CBD1</t>
+          <t>OPM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-IV</t>
+          <t>QCSP_001_OPM-V</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>+0.39 / −1.40</t>
+          <t>±1.10</t>
         </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>12.6</v>
+        <v>10.9</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>14.39</v>
+        <v>13.1</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>14.00% +0.39%/−1.40% (12.60% — 14.39%)</t>
+          <t>12.00% ±1.10% (10.90% — 13.10%)</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>RESERVE (contiguity bridge)</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>OPM052501 14.16</t>
+          <t>— reserve grade (no current batch)</t>
         </is>
       </c>
     </row>
@@ -3091,49 +3091,49 @@
       <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC12 : CBD1</t>
+          <t>OPM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-V</t>
+          <t>QCSP_001_OPM-VI</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>+0.59 / −1.20</t>
+          <t>±0.89</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>10.8</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>12.59</v>
+        <v>10.89</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>12.00% +0.59%/−1.20% (10.80% — 12.59%)</t>
+          <t>10.00% ±0.89% (9.11% — 10.89%)</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>RESERVE (contiguity bridge)</t>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>— reserve grade (no current batch)</t>
+          <t>OPM092501 9.43</t>
         </is>
       </c>
     </row>
@@ -3142,159 +3142,159 @@
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>VII</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC10 : CBD1</t>
+          <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-VI</t>
+          <t>QCSP_001_OPM-VII</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>+0.79 / −1.00</t>
+          <t>±0.80</t>
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>10.79</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>10.00% +0.79%/−1.00% (9.00% — 10.79%)</t>
-        </is>
-      </c>
-      <c r="L52" s="9" t="inlineStr">
+          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
+        </is>
+      </c>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>OPM112501 8.00, OPM122501 7.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>PM_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_PM-I</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
         <is>
           <t>clipped (contiguity rule)</t>
         </is>
       </c>
-      <c r="M52" s="7" t="inlineStr">
-        <is>
-          <t>OPM092501 9.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr"/>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>VII</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>OPM_THC8 : CBD1</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_OPM-VII</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>±0.80</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>OPM112501 8.00, OPM122501 7.91</t>
+          <t>PM112501 13.33</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Permanent Marker</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
+      <c r="A54" s="7" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr"/>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>PM_THC14 : CBD1</t>
+          <t>PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-I</t>
+          <t>QCSP_001_PM-II</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>±1.40</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>12.6</v>
+        <v>11.01</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>15.4</v>
+        <v>12.99</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±1.40% (12.60% — 15.40%)</t>
-        </is>
-      </c>
-      <c r="L54" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>12.00% ±0.99% (11.01% — 12.99%)</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>PM112501 13.33</t>
+          <t>PM092501 12.25</t>
         </is>
       </c>
     </row>
@@ -3303,112 +3303,120 @@
       <c r="B55" s="5" t="inlineStr"/>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>PM_THC12 : CBD1</t>
+          <t>PM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-II</t>
+          <t>QCSP_001_PM-III</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>+0.59 / −1.20</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>12.59</v>
+        <v>11</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>12.00% +0.59%/−1.20% (10.80% — 12.59%)</t>
-        </is>
-      </c>
-      <c r="L55" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>PM092501 12.25</t>
+          <t>PM072501 10.01</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr"/>
-      <c r="B56" s="5" t="inlineStr"/>
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>PUM</t>
+        </is>
+      </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>PM_THC10 : CBD1</t>
+          <t>PUM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-III</t>
+          <t>QCSP_001_PUM-I</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>+0.79 / −1.00</t>
+          <t>±1.60</t>
         </is>
       </c>
       <c r="H56" s="6" t="n">
-        <v>9</v>
+        <v>14.4</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>10.79</v>
+        <v>17.6</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>10.00% +0.79%/−1.00% (9.00% — 10.79%)</t>
-        </is>
-      </c>
-      <c r="L56" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>PM072501 10.01</t>
+          <t>PUM102501 15.63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>PUM</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3418,34 +3426,34 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>PUM_THC16 : CBD1</t>
+          <t>SCR_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PUM-I</t>
+          <t>QCSP_001_SCR-I</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>±1.60</t>
+          <t>±2.20</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>14.4</v>
+        <v>19.8</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>17.6</v>
+        <v>24.2</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
         </is>
       </c>
       <c r="L57" s="8" t="inlineStr">
@@ -3455,239 +3463,239 @@
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>PUM102501 15.63</t>
+          <t>SCR022601 21.92</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>SCR</t>
-        </is>
-      </c>
+      <c r="A58" s="7" t="inlineStr"/>
+      <c r="B58" s="5" t="inlineStr"/>
       <c r="C58" s="5" t="inlineStr">
         <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>SCR_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SCR-II</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>±1.79</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.79% (16.21% — 19.79%)</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>SCR_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SCR-I</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="n">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>SJ_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SJ-I</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>±1.03</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>12.00% ±1.03% (10.97% — 13.03%)</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>SJ102501 11.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>SJ_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SJ-II</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>±0.96</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>10.00% ±0.96% (9.04% — 10.96%)</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>clipped (contiguity rule)</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>SJ092501 10.96, SJ112501 9.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>WED</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>WED_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_WED-I</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>±2.20</t>
         </is>
       </c>
-      <c r="H58" s="6" t="n">
+      <c r="H61" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="I58" s="6" t="n">
+      <c r="I61" s="6" t="n">
         <v>24.2</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="J61" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="K61" s="7" t="inlineStr">
         <is>
           <t>22.00% ±2.20% (19.80% — 24.20%)</t>
         </is>
       </c>
-      <c r="L58" s="8" t="inlineStr">
+      <c r="L61" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="M58" s="7" t="inlineStr">
-        <is>
-          <t>SCR022601 21.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr"/>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>SCR_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SCR-II</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>+1.79 / −1.80</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I59" s="6" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>18.00% +1.79%/−1.80% (16.20% — 19.79%)</t>
-        </is>
-      </c>
-      <c r="L59" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Sleepy Joy</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>SJ_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SJ-I</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>+1.20 / −1.03</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>12.00% +1.20%/−1.03% (10.97% — 13.20%)</t>
-        </is>
-      </c>
-      <c r="L60" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>SJ102501 11.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr"/>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>SJ_THC10 : CBD1</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SJ-II</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>+0.96 / −1.00</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="I61" s="6" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>10.00% +0.96%/−1.00% (9.00% — 10.96%)</t>
-        </is>
-      </c>
-      <c r="L61" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>SJ092501 10.96, SJ112501 9.20</t>
+          <t>WED102501 22.05</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>WED</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3697,12 +3705,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>WED_THC22 : CBD1</t>
+          <t>WC_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_WED-I</t>
+          <t>QCSP_001_WC-I</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
@@ -3733,65 +3741,6 @@
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
-        <is>
-          <t>WED102501 22.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Wedding Crasher</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>WC</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>WC_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_WC-I</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>±2.20</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I63" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L63" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M63" s="7" t="inlineStr">
         <is>
           <t>WC072501 22.11, WC082501 21.67</t>
         </is>
@@ -4297,7 +4246,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC22 : CBD1</t>
+          <t>CJ_THC21 : CBD1</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
@@ -4333,7 +4282,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC20 : CBD1</t>
+          <t>CJ_THC19 : CBD1</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
@@ -4373,7 +4322,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC20 : CBD1</t>
+          <t>CJ_THC19 : CBD1</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
@@ -4404,12 +4353,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC14 : CBD1</t>
+          <t>CJ_THC15 : CBD1</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
@@ -4645,7 +4594,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>FB_THC20 : CBD1</t>
+          <t>FB_THC21 : CBD1</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
@@ -5145,7 +5094,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC25 : CBD1</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
@@ -5185,7 +5134,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC25 : CBD1</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
@@ -5221,7 +5170,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC25 : CBD1</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
@@ -5261,7 +5210,7 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC25 : CBD1</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
@@ -5297,7 +5246,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC25 : CBD1</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
@@ -5337,7 +5286,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC25 : CBD1</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
@@ -5377,7 +5326,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC25 : CBD1</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
@@ -5408,7 +5357,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -5448,7 +5397,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -5484,7 +5433,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -5524,7 +5473,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -5560,7 +5509,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -5596,7 +5545,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -5821,7 +5770,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>JD_THC20 : CBD1</t>
+          <t>JD_THC19 : CBD1</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
@@ -5857,7 +5806,7 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>JD_THC20 : CBD1</t>
+          <t>JD_THC19 : CBD1</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
@@ -5893,7 +5842,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>JD_THC20 : CBD1</t>
+          <t>JD_THC19 : CBD1</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
@@ -5933,7 +5882,7 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>JD_THC20 : CBD1</t>
+          <t>JD_THC19 : CBD1</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
@@ -5968,7 +5917,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -6008,7 +5957,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -6044,7 +5993,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -6317,7 +6266,7 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>OPM_THC22 : CBD1</t>
+          <t>OPM_THC21 : CBD1</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
@@ -7146,7 +7095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7193,7 +7142,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ranges within one strain do not overlap. The strongest grade is given the maximum range first; each weaker grade takes the widest window that remains. Where an even nominal two steps down must still contain its own nominal value, the stronger grade cedes the minimum necessary from the bottom of its window (this is why some strong-grade lower bounds sit above 0.90 x nominal).</t>
+          <t>SYMMETRIC tolerance (management rule, 27.08.2026): every grade is nominal ± t with the SAME t above and below, so the window is always centred on the nominal. Contiguity then binds neighbouring grades by the equality t_upper + t_lower = (N_upper - N_lower) - 0.01, which chains every tolerance to the top grade of the ladder.</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7154,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Every batch of the strain falls inside exactly one grade window at its latest certified Total THC value (register CoQ-forming value).</t>
+          <t>Ranges within one strain do not overlap; the strongest grade is given the maximum tolerance the chain allows first, each weaker grade takes what the equalities leave.</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7166,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Retest results are the CoQ-forming anchors (management rule, 27.08.2026): where a batch has a retest (Tranche 1 197-series of 07.08.2026, the April J31 retests, and the pending Tranche 2 re-analysis when it lands), the grade is designed on the retest value; superseded pre-retest results are out of specification scope.</t>
+          <t>Every batch of the strain falls inside exactly one grade window at its latest certified Total THC value (retest = CoQ-forming; superseded pre-retest results are out of scope).</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7178,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Contiguity (management rule, 27.08.2026): from the top grade down, consecutive grade ranges join without gap or overlap (upper of the weaker = lower of the stronger minus 0.01). Where batch-bearing grades cannot join directly, RESERVE grades (spec-defined, no current batch) are inserted to close the span. Sole exception: below 10% THC, where the ladder mathematically cannot join, the lowest grade(s) may sit with a documented uncovered zone above them (GRC 7.71-10.79; OPM 8.81-8.99).</t>
+          <t>Contiguity: from the top grade down, consecutive ranges join at 0.01. RESERVE grades (spec-defined, no current batch) close spans that batch-bearing grades cannot bridge. Sole exception below 10% THC where no meaningful symmetric ladder joins: the lowest grade(s) sit with a documented uncovered zone (GRC 7.71-10.79; OPM 8.81-9.10).</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7190,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ODD-nominal fallback (management rule, 27.08.2026): an isolated result that no even nominal can hold within ±10% (the even ladder has dead zones at 6.61–7.19 and 8.81–8.99) takes the adjacent ODD whole-number nominal instead, formed without overlap against the neighbouring ranges. With this fallback every result above ≈5.0% THC is always placeable (for any value v, at least one whole number lies between v/1.1 and v/0.9 once v ≥ 5).</t>
+          <t>ODD-nominal adjustment (management rule, 27.08.2026): where the initially selected even nominal cannot carry a symmetric window under rules 2-6, the nominal shifts to the adjacent odd whole number (above or below). Also covers isolated results in the even ladder dead zones (GRC_THC7). No grade tolerance is allowed below 0.50 (a 0.40pp-wide grade is not a meaningful specification).</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7214,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme / GRC102501/1: 7.05 fits no even nominal (even-ladder dead zone) -&gt; ODD fallback THC7 [6.30-7.70]</t>
+          <t>Cap Junky: THC22 -&gt; THC21 (odd shift for symmetric tolerance) [owner-coded]: CJ062501/1</t>
         </is>
       </c>
     </row>
@@ -7277,21 +7226,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Permanent Marker / PM112501: owner code THC12 infeasible for 13.33 (max window 10.80-13.20) -&gt; THC14</t>
+          <t>Cap Junky: THC20 -&gt; THC19 (odd shift for symmetric tolerance) [owner-coded]: CJ062501/2, CJ082501/2</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Cap Junky: THC14 -&gt; THC15 (odd shift for symmetric tolerance): CJ052501/02</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>EXCEPTIONS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr"/>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard: THC20 -&gt; THC21 (odd shift for symmetric tolerance): FB012603</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -7301,7 +7262,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme: uncovered zone 7.71-10.79 between THC12 and THC7 (sub-10% territory — even ladder cannot join; permitted per rule)</t>
+          <t>Grape Pie: THC24 -&gt; THC25 (odd shift for symmetric tolerance) [owner-coded]: P160012, GP092501, P160022, GP0824_03, GP062501, P160032, GP0824_02</t>
         </is>
       </c>
     </row>
@@ -7313,21 +7274,33 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa: uncovered zone 8.81-8.99 between THC10 and THC8 (sub-10% territory — even ladder cannot join; permitted per rule)</t>
+          <t>Graps &amp; Creme / GRC102501/1: 7.05 fits no even nominal (even-ladder dead zone) -&gt; ODD fallback THC7 [6.30-7.70]</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Jelly Donutz: THC20 -&gt; THC19 (odd shift for symmetric tolerance) [owner-coded]: JD012603/02, JD112501, JD022601, JD012601*</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>OPEN VERIFICATIONS CARRIED OVER</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa: THC22 -&gt; THC21 (odd shift for symmetric tolerance) [owner-coded]: OPM1024</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -7337,33 +7310,21 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
+          <t>Permanent Marker / PM112501: owner code THC12 infeasible for 13.33 (max window 10.80-13.20) -&gt; THC14</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
-        </is>
-      </c>
+      <c r="A20" s="14" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
-        </is>
-      </c>
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>EXCEPTIONS</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -7373,7 +7334,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+          <t>Graps &amp; Creme: uncovered zone 7.71-10.79 between THC12 and THC7 (sub-10% territory — ladder cannot join symmetrically; permitted per rule)</t>
         </is>
       </c>
     </row>
@@ -7385,33 +7346,21 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+          <t>Orange Punch Mimosa: uncovered zone 8.81-9.10 between THC10 and THC8 (sub-10% territory — ladder cannot join symmetrically; permitted per rule)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Truth-check finding (27.08.2026): certificate ППК26065 (13.93, CNP, 11.05.2026) prints серија JD112501* — the milled Jelly Donutz presentation, a separate register batch — and was misattributed to JD112501 (whole flower, retest 20.32) in the source dataset. Reattributed; JD112501* now carries its own grade JD_THC14:CBD1 (12.60 — 14.39).</t>
-        </is>
-      </c>
+      <c r="A24" s="14" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Grades whose upper bound is pinned by the grade above print +0.00% up-tolerance (CJ-II, CJ-III, CJ-IV): the nominal sits at the very top of its window — the mathematically forced consequence of the strongest-first maximum-range rule with even nominals two steps apart. Management may instead grant each such grade a small up-headroom at the cost of the grade above; flag for decision if the +0.00 display is unacceptable.</t>
-        </is>
-      </c>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>OPEN VERIFICATIONS CARRIED OVER</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -7420,6 +7369,78 @@
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Truth-check finding (27.08.2026): certificate ППК26065 (13.93, CNP, 11.05.2026) prints серија JD112501* — the milled Jelly Donutz presentation, a separate register batch — and was misattributed to JD112501 (whole flower, retest 20.32) in the source dataset. Reattributed; JD112501* now carries its own grade JD_THC14:CBD1 (12.60 — 14.39).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Batches on declared values (no eCoA yet): ACC102501, CC012603, CF102501, JD012603/01, PUM102501 (T2 re-analysis sampled 12.08.2026, results pending), SCR012601, WED102501, JD022601, GRC102501/1, P160012, P160022, P160032 — their grades are provisional.</t>
         </is>

--- a/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
+++ b/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rules: nominal = whole even number (adjacent odd only where symmetry is impossible); tolerance EQUAL above and below the nominal, at most 10% of it; two-decimal bounds; no overlap; contiguous ladders; strongest grade takes the maximum range first; every batch falls in exactly one grade.</t>
+          <t>Rules: whole even nominal preferred (odd only where no even configuration works); tolerance EQUAL above and below the nominal, at most 10% of it; NO empty grades — result-free spans stay as documented gaps; touching grades split their budget as equally as the constraints allow; every batch falls in exactly one grade.</t>
         </is>
       </c>
     </row>
@@ -804,26 +804,26 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>±2.40</t>
+          <t>±1.99</t>
         </is>
       </c>
       <c r="H8" s="6" t="n">
-        <v>21.6</v>
+        <v>22.01</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>26.4</v>
+        <v>25.99</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>24.00% ±2.40% (21.60% — 26.40%)</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>24.00% ±1.99% (22.01% — 25.99%)</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -855,26 +855,26 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>±1.59</t>
+          <t>±2.00</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18.41</v>
+        <v>18</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>21.59</v>
+        <v>22</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>20.00% ±1.59% (18.41% — 21.59%)</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>20.00% ±2.00% (18.00% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -914,26 +914,26 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>±2.40</t>
+          <t>±1.99</t>
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>21.6</v>
+        <v>22.01</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>26.4</v>
+        <v>25.99</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>24.00% ±2.40% (21.60% — 26.40%)</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>24.00% ±1.99% (22.01% — 25.99%)</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC21 : CBD1</t>
+          <t>CJ_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -961,35 +961,35 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>±0.59</t>
+          <t>±2.00</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>20.41</v>
+        <v>18</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>21.59</v>
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>21.00% ±0.59% (20.41% — 21.59%)</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
+          <t>20.00% ±2.00% (18.00% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>CJ062501/1 21.51</t>
+          <t>CJ062501/1 21.51, CJ062501/2 18.91, CJ082501/2 18.29</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC19 : CBD1</t>
+          <t>CJ_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1012,86 +1012,94 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>±1.40</t>
+          <t>±1.60</t>
         </is>
       </c>
       <c r="H12" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>17.6</v>
       </c>
-      <c r="I12" s="6" t="n">
-        <v>20.4</v>
-      </c>
       <c r="J12" s="6" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>19.00% ±1.40% (17.60% — 20.40%)</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
+          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>CJ062501/2 18.91, CJ082501/2 18.29</t>
+          <t>CJ052501/02 14.93</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC17 : CBD1</t>
+          <t>CC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-IV</t>
+          <t>QCSP_001_CC-I</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>±0.59</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>16.41</v>
+        <v>16.2</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>17.59</v>
+        <v>19.8</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>1.18</v>
+        <v>3.6</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>17.00% ±0.59% (16.41% — 17.59%)</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>RESERVE (contiguity bridge) — ODD nominal (fallback rule 5)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>— reserve grade (no current batch)</t>
+          <t>CC012601/1 17.67</t>
         </is>
       </c>
     </row>
@@ -1100,457 +1108,457 @@
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC15 : CBD1</t>
+          <t>CC_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-V</t>
+          <t>QCSP_001_CC-II</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>±1.40</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>13.6</v>
+        <v>13.01</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>16.4</v>
+        <v>14.99</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>15.00% ±1.40% (13.60% — 16.40%)</t>
+          <t>14.00% ±0.99% (13.01% — 14.99%)</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>CJ052501/02 14.93</t>
+          <t>CC112501 13.35</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Cash Cow</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CC_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CC-III</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>12.00% ±1.00% (11.00% — 13.00%)</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>CC012603 12.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>CC_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC-I</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>CF_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CF-I</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>CF102501 9.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>CLE_THC8 : CBD1</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CLE-I</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>±0.80</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>CLE072501 8.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>FB_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_FB-I</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>±2.19</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>FB012603 20.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>FB_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_FB-II</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>±1.40</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.40% (16.60% — 19.40%)</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>CC012601/1 17.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>CC_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC-II</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>±0.59</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>16.59</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>16.00% ±0.59% (15.41% — 16.59%)</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>RESERVE (contiguity bridge)</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>— reserve grade (no current batch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>±1.80</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>III</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>CC_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC-III</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>FB_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_FB-III</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>±1.40</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>14.00% ±1.40% (12.60% — 15.40%)</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>CC112501 13.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>±0.99</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>14.00% ±0.99% (13.01% — 14.99%)</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>FB012601/1 14.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>CC_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC-IV</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>FB_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_FB-IV</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>±0.59</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>12.00% ±0.59% (11.41% — 12.59%)</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>CC012603 12.32</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Chem Flyer</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>12.00% ±1.00% (11.00% — 13.00%)</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>FB032601 12.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>CF_THC10 : CBD1</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CF-I</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>±1.00</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>CF102501 9.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Clemosa a bud</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>CLE_THC8 : CBD1</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CLE-I</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>±0.80</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>CLE072501 8.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>FB</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>FB_THC21 : CBD1</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_FB-I</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>±1.68</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>19.32</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>22.68</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>21.00% ±1.68% (19.32% — 22.68%)</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>FB012603 20.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>FB_THC18 : CBD1</t>
+          <t>GG_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-II</t>
+          <t>QCSP_001_GG-I</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1558,31 +1566,31 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>±1.31</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>16.69</v>
+        <v>17</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>19.31</v>
+        <v>19</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.31% (16.69% — 19.31%)</t>
+          <t>18.00% ±1.00% (17.00% — 19.00%)</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
+          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
         </is>
       </c>
     </row>
@@ -1591,17 +1599,17 @@
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>FB_THC16 : CBD1</t>
+          <t>GG_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-III</t>
+          <t>QCSP_001_GG-II</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -1609,31 +1617,31 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>±0.68</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>15.32</v>
+        <v>15.01</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>16.68</v>
+        <v>16.99</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±0.68% (15.32% — 16.68%)</t>
+          <t>16.00% ±0.99% (15.01% — 16.99%)</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>RESERVE (contiguity bridge)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>— reserve grade (no current batch)</t>
+          <t>GG012603 16.70, GG1024_02 15.95, GG012601* 15.35</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1650,17 @@
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>FB_THC14 : CBD1</t>
+          <t>GG_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-IV</t>
+          <t>QCSP_001_GG-III</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -1660,141 +1668,141 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>±1.31</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
-        <v>12.69</v>
+        <v>13</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>15.31</v>
+        <v>15</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±1.31% (12.69% — 15.31%)</t>
+          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>FB012601/1 14.68</t>
+          <t>GG1024 13.34</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>FB_THC12 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-V</t>
+          <t>QCSP_001_GP-I</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>±0.68</t>
+          <t>±2.40</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>11.32</v>
+        <v>21.6</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>12.68</v>
+        <v>26.4</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>12.00% ±0.68% (11.32% — 12.68%)</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>24.00% ±2.40% (21.60% — 26.40%)</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>FB032601 12.39</t>
+          <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>GG</t>
-        </is>
-      </c>
+      <c r="A26" s="7" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>GG_THC18 : CBD1</t>
+          <t>GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-I</t>
+          <t>QCSP_001_GP-II</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>±1.29</t>
+          <t>±1.36</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>16.71</v>
+        <v>18.64</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>19.29</v>
+        <v>21.36</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.29% (16.71% — 19.29%)</t>
+          <t>20.00% ±1.36% (18.64% — 21.36%)</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
+          <t>GP072501/1 21.36, GP082501/1 21.29, GP0824_01 20.79, GP072501/2 19.81</t>
         </is>
       </c>
     </row>
@@ -1803,49 +1811,49 @@
       <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>GG_THC16 : CBD1</t>
+          <t>GP_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-II</t>
+          <t>QCSP_001_GP-III</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>±0.70</t>
+          <t>±0.63</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>15.3</v>
+        <v>17.37</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>16.7</v>
+        <v>18.63</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±0.70% (15.30% — 16.70%)</t>
+          <t>18.00% ±0.63% (17.37% — 18.63%)</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>GG012603 16.70, GG1024_02 15.95, GG012601* 15.35</t>
+          <t>GP052501 18.52</t>
         </is>
       </c>
     </row>
@@ -1854,61 +1862,61 @@
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>GG_THC14 : CBD1</t>
+          <t>GP_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-III</t>
+          <t>QCSP_001_GP-IV</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>±1.29</t>
+          <t>±1.36</t>
         </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>12.71</v>
+        <v>14.64</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>15.29</v>
+        <v>17.36</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±1.29% (12.71% — 15.29%)</t>
+          <t>16.00% ±1.36% (14.64% — 17.36%)</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>GG1024 13.34</t>
+          <t>GP082501/2 15.70</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1918,44 +1926,44 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>GP_THC25 : CBD1</t>
+          <t>GRC_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-I</t>
+          <t>QCSP_001_GRC-I</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>±2.47</t>
+          <t>±1.20</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>22.53</v>
+        <v>10.8</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>27.47</v>
+        <v>13.2</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4.94</v>
+        <v>2.4</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>25.00% ±2.47% (22.53% — 27.47%)</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule) — ODD nominal (fallback rule 5)</t>
+          <t>12.00% ±1.20% (10.80% — 13.20%)</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
+          <t>GRC102501/2 11.53</t>
         </is>
       </c>
     </row>
@@ -1969,95 +1977,103 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>GP_THC22 : CBD1</t>
+          <t>GRC_THC7 : CBD1</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-II</t>
+          <t>QCSP_001_GRC-II</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>±0.70</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>7.00% ±0.70% (6.30% — 7.70%)</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>GRC102501/1 7.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>HPA</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>HPA_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_HPA-I</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>±0.52</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>22.52</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±0.52% (21.48% — 22.52%)</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>RESERVE (contiguity bridge)</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>— reserve grade (no current batch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr"/>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>GP_THC20 : CBD1</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GP-III</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>20</v>
-      </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>±1.47</t>
+          <t>±2.19</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>18.53</v>
+        <v>19.81</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>21.47</v>
+        <v>24.19</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>2.94</v>
+        <v>4.38</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>20.00% ±1.47% (18.53% — 21.47%)</t>
+          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>GP072501/1 21.36, GP082501/1 21.29, GP0824_01 20.79, GP072501/2 19.81</t>
+          <t>HPA1024_01 21.61, HPA052501 20.39</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2082,17 @@
       <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>GP_THC18 : CBD1</t>
+          <t>HPA_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-IV</t>
+          <t>QCSP_001_HPA-II</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
@@ -2084,141 +2100,141 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>±0.52</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>17.48</v>
+        <v>16.2</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>18.52</v>
+        <v>19.8</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±0.52% (17.48% — 18.52%)</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>GP052501 18.52</t>
+          <t>HPA1024 17.31</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr"/>
-      <c r="B33" s="5" t="inlineStr"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>GP_THC16 : CBD1</t>
+          <t>JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-V</t>
+          <t>QCSP_001_JD-I</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>±2.00</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>20.00% ±2.00% (18.00% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601* 18.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>JD_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_JD-II</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>±1.47</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>14.53</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>16.00% ±1.47% (14.53% — 17.47%)</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="inlineStr">
-        <is>
-          <t>GP082501/2 15.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Graps &amp; Creme</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>GRC</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>GRC_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GRC-I</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>12</v>
-      </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>±1.20</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H34" s="6" t="n">
-        <v>10.8</v>
+        <v>15.01</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>13.2</v>
+        <v>16.99</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>12.00% ±1.20% (10.80% — 13.20%)</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>16.00% ±0.99% (15.01% — 16.99%)</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>GRC102501/2 11.53</t>
+          <t>JD012603/01 16.71, JD012603/02V 15.16</t>
         </is>
       </c>
     </row>
@@ -2227,61 +2243,61 @@
       <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>GRC_THC7 : CBD1</t>
+          <t>JD_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GRC-II</t>
+          <t>QCSP_001_JD-III</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>±0.70</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>6.3</v>
+        <v>13</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>7.7</v>
+        <v>15</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>7.00% ±0.70% (6.30% — 7.70%)</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
+          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>GRC102501/1 7.05</t>
+          <t>JD112501* 13.93</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>HPA</t>
+          <t>J31</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2291,12 +2307,12 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>HPA_THC22 : CBD1</t>
+          <t>J31_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_HPA-I</t>
+          <t>QCSP_001_J31-I</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -2304,31 +2320,31 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>±2.20</t>
+          <t>±2.19</t>
         </is>
       </c>
       <c r="H36" s="6" t="n">
-        <v>19.8</v>
+        <v>19.81</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>24.2</v>
+        <v>24.19</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>HPA1024_01 21.61, HPA052501 20.39</t>
+          <t>J31122501 21.84, J31112501 20.21</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2358,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>HPA_THC18 : CBD1</t>
+          <t>J31_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_HPA-II</t>
+          <t>QCSP_001_J31-II</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -2355,43 +2371,43 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>±1.79</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>16.21</v>
+        <v>16.2</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.79% (16.21% — 19.79%)</t>
-        </is>
-      </c>
-      <c r="L37" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>HPA1024 17.31</t>
+          <t>J31102501 17.32</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2401,95 +2417,103 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>JD_THC19 : CBD1</t>
+          <t>KC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-I</t>
+          <t>QCSP_001_KC-I</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>±1.90</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>17.1</v>
+        <v>16.2</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>20.9</v>
+        <v>19.8</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>19.00% ±1.90% (17.10% — 20.90%)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601* 18.16</t>
+          <t>KC102501 17.04</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>JD_THC16 : CBD1</t>
+          <t>MB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-II</t>
+          <t>QCSP_001_MB-I</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>±1.09</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>14.91</v>
+        <v>17.01</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>17.09</v>
+        <v>18.99</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±1.09% (14.91% — 17.09%)</t>
+          <t>18.00% ±0.99% (17.01% — 18.99%)</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>JD012603/01 16.71, JD012603/02V 15.16</t>
+          <t>MB0824_04 18.67</t>
         </is>
       </c>
     </row>
@@ -2498,61 +2522,61 @@
       <c r="B40" s="5" t="inlineStr"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>JD_THC14 : CBD1</t>
+          <t>MB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-III</t>
+          <t>QCSP_001_MB-II</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>±0.90</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H40" s="6" t="n">
-        <v>13.1</v>
+        <v>15</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±0.90% (13.10% — 14.90%)</t>
+          <t>16.00% ±1.00% (15.00% — 17.00%)</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>JD112501* 13.93</t>
+          <t>MB0824_05 16.82</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>J31</t>
+          <t>OPM</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2562,12 +2586,12 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>J31_THC22 : CBD1</t>
+          <t>OPM_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_J31-I</t>
+          <t>QCSP_001_OPM-I</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
@@ -2599,7 +2623,7 @@
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>J31122501 21.84, J31112501 20.21</t>
+          <t>OPM1024 20.03</t>
         </is>
       </c>
     </row>
@@ -2613,12 +2637,12 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>J31_THC18 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_J31-II</t>
+          <t>QCSP_001_OPM-II</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -2626,149 +2650,133 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>±1.79</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H42" s="6" t="n">
-        <v>16.21</v>
+        <v>17</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>19.79</v>
+        <v>19</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>3.58</v>
+        <v>2</v>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.79% (16.21% — 19.79%)</t>
+          <t>18.00% ±1.00% (17.00% — 19.00%)</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>J31102501 17.32</t>
+          <t>OPM1024_02 18.04</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Kush Crasher</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
+      <c r="A43" s="7" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>KC_THC18 : CBD1</t>
+          <t>OPM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_KC-I</t>
+          <t>QCSP_001_OPM-III</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>±1.80</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>16.2</v>
+        <v>15.01</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>19.8</v>
+        <v>16.99</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>3.6</v>
+        <v>1.98</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>16.00% ±0.99% (15.01% — 16.99%)</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>KC102501 17.04</t>
+          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Motor Breath</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
+      <c r="A44" s="7" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>MB_THC18 : CBD1</t>
+          <t>OPM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-I</t>
+          <t>QCSP_001_OPM-IV</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>±1.17</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H44" s="6" t="n">
-        <v>16.83</v>
+        <v>13</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>19.17</v>
+        <v>15</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.17% (16.83% — 19.17%)</t>
+          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>MB0824_04 18.67</t>
+          <t>OPM052501 14.16</t>
         </is>
       </c>
     </row>
@@ -2777,159 +2785,159 @@
       <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>MB_THC16 : CBD1</t>
+          <t>OPM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-II</t>
+          <t>QCSP_001_OPM-V</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>±0.82</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>15.18</v>
+        <v>9</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>16.82</v>
+        <v>11</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±0.82% (15.18% — 16.82%)</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>MB0824_05 16.82</t>
+          <t>OPM092501 9.43</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>OPM</t>
-        </is>
-      </c>
+      <c r="A46" s="7" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>OPM_THC8 : CBD1</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_OPM-VI</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>±0.80</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>OPM112501 8.00, OPM122501 7.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>OPM_THC21 : CBD1</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_OPM-I</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>±2.10</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>21.00% ±2.10% (18.90% — 23.10%)</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>OPM1024 20.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC18 : CBD1</t>
+          <t>PM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-II</t>
+          <t>QCSP_001_PM-I</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>±0.89</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>17.11</v>
+        <v>13</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>18.89</v>
+        <v>15</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±0.89% (17.11% — 18.89%)</t>
+          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>OPM1024_02 18.04</t>
+          <t>PM112501 13.33</t>
         </is>
       </c>
     </row>
@@ -2938,49 +2946,49 @@
       <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-III</t>
+          <t>QCSP_001_PM-II</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>±1.10</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>14.9</v>
+        <v>11.01</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>17.1</v>
+        <v>12.99</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±1.10% (14.90% — 17.10%)</t>
+          <t>12.00% ±0.99% (11.01% — 12.99%)</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
+          <t>PM092501 12.25</t>
         </is>
       </c>
     </row>
@@ -2989,151 +2997,167 @@
       <c r="B49" s="5" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC14 : CBD1</t>
+          <t>PM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-IV</t>
+          <t>QCSP_001_PM-III</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>±0.89</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>13.11</v>
+        <v>9</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>14.89</v>
+        <v>11</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±0.89% (13.11% — 14.89%)</t>
-        </is>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>OPM052501 14.16</t>
+          <t>PM072501 10.01</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr"/>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>PUM</t>
+        </is>
+      </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC12 : CBD1</t>
+          <t>PUM_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-V</t>
+          <t>QCSP_001_PUM-I</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>±1.10</t>
+          <t>±1.60</t>
         </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>10.9</v>
+        <v>14.4</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>13.1</v>
+        <v>17.6</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>12.00% ±1.10% (10.90% — 13.10%)</t>
-        </is>
-      </c>
-      <c r="L50" s="9" t="inlineStr">
-        <is>
-          <t>RESERVE (contiguity bridge)</t>
+          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>— reserve grade (no current batch)</t>
+          <t>PUM102501 15.63</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr"/>
-      <c r="B51" s="5" t="inlineStr"/>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>SCR</t>
+        </is>
+      </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC10 : CBD1</t>
+          <t>SCR_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-VI</t>
+          <t>QCSP_001_SCR-I</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>±0.89</t>
+          <t>±2.19</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>9.109999999999999</v>
+        <v>19.81</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>10.89</v>
+        <v>24.19</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.78</v>
+        <v>4.38</v>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>10.00% ±0.89% (9.11% — 10.89%)</t>
+          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>OPM092501 9.43</t>
+          <t>SCR022601 21.92</t>
         </is>
       </c>
     </row>
@@ -3142,39 +3166,39 @@
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC8 : CBD1</t>
+          <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-VII</t>
+          <t>QCSP_001_SCR-II</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>±0.80</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>7.2</v>
+        <v>16.2</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
@@ -3184,19 +3208,19 @@
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>OPM112501 8.00, OPM122501 7.91</t>
+          <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3206,44 +3230,44 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>PM_THC14 : CBD1</t>
+          <t>SJ_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-I</t>
+          <t>QCSP_001_SJ-I</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>±1.00</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>13</v>
+        <v>11.01</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>15</v>
+        <v>12.99</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
+          <t>12.00% ±0.99% (11.01% — 12.99%)</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>clipped (contiguity rule)</t>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>PM112501 13.33</t>
+          <t>SJ102501 11.20</t>
         </is>
       </c>
     </row>
@@ -3257,85 +3281,93 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>PM_THC12 : CBD1</t>
+          <t>SJ_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-II</t>
+          <t>QCSP_001_SJ-II</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>±0.99</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>11.01</v>
+        <v>9</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>12.99</v>
+        <v>11</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>12.00% ±0.99% (11.01% — 12.99%)</t>
-        </is>
-      </c>
-      <c r="L54" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>PM092501 12.25</t>
+          <t>SJ092501 10.96, SJ112501 9.20</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr"/>
-      <c r="B55" s="5" t="inlineStr"/>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>WED</t>
+        </is>
+      </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>PM_THC10 : CBD1</t>
+          <t>WED_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-III</t>
+          <t>QCSP_001_WED-I</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>±1.00</t>
+          <t>±2.20</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>9</v>
+        <v>19.8</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>11</v>
+        <v>24.2</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr">
@@ -3345,19 +3377,19 @@
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>PM072501 10.01</t>
+          <t>WED102501 22.05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>PUM</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -3367,34 +3399,34 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>PUM_THC16 : CBD1</t>
+          <t>WC_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PUM-I</t>
+          <t>QCSP_001_WC-I</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>±1.60</t>
+          <t>±2.20</t>
         </is>
       </c>
       <c r="H56" s="6" t="n">
-        <v>14.4</v>
+        <v>19.8</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>17.6</v>
+        <v>24.2</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
         </is>
       </c>
       <c r="L56" s="8" t="inlineStr">
@@ -3403,344 +3435,6 @@
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
-        <is>
-          <t>PUM102501 15.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>SCR</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>SCR_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SCR-I</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>±2.20</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L57" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>SCR022601 21.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr"/>
-      <c r="B58" s="5" t="inlineStr"/>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>SCR_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SCR-II</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>±1.79</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.79% (16.21% — 19.79%)</t>
-        </is>
-      </c>
-      <c r="L58" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M58" s="7" t="inlineStr">
-        <is>
-          <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Sleepy Joy</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>SJ_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SJ-I</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>±1.03</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="I59" s="6" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>12.00% ±1.03% (10.97% — 13.03%)</t>
-        </is>
-      </c>
-      <c r="L59" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>SJ102501 11.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr"/>
-      <c r="B60" s="5" t="inlineStr"/>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>SJ_THC10 : CBD1</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SJ-II</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>±0.96</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>10.00% ±0.96% (9.04% — 10.96%)</t>
-        </is>
-      </c>
-      <c r="L60" s="9" t="inlineStr">
-        <is>
-          <t>clipped (contiguity rule)</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>SJ092501 10.96, SJ112501 9.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Wedding Cake</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>WED</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>WED_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_WED-I</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>±2.20</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I61" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L61" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>WED102501 22.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Wedding Crasher</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>WC</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>WC_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_WC-I</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>±2.20</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I62" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L62" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M62" s="7" t="inlineStr">
         <is>
           <t>WC072501 22.11, WC082501 21.67</t>
         </is>
@@ -4246,7 +3940,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC21 : CBD1</t>
+          <t>CJ_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
@@ -4277,12 +3971,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC19 : CBD1</t>
+          <t>CJ_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
@@ -4317,12 +4011,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC19 : CBD1</t>
+          <t>CJ_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
@@ -4353,12 +4047,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC15 : CBD1</t>
+          <t>CJ_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
@@ -4433,7 +4127,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -4473,7 +4167,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -4594,7 +4288,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>FB_THC21 : CBD1</t>
+          <t>FB_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
@@ -4745,7 +4439,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -4781,7 +4475,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -5094,7 +4788,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>GP_THC25 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
@@ -5134,7 +4828,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>GP_THC25 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
@@ -5170,7 +4864,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>GP_THC25 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
@@ -5210,7 +4904,7 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>GP_THC25 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
@@ -5246,7 +4940,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>GP_THC25 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
@@ -5286,7 +4980,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>GP_THC25 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
@@ -5326,7 +5020,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>GP_THC25 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
@@ -5357,7 +5051,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -5397,7 +5091,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -5433,7 +5127,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -5473,7 +5167,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -5509,7 +5203,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -5545,7 +5239,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -5770,7 +5464,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>JD_THC19 : CBD1</t>
+          <t>JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
@@ -5806,7 +5500,7 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>JD_THC19 : CBD1</t>
+          <t>JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
@@ -5842,7 +5536,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>JD_THC19 : CBD1</t>
+          <t>JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
@@ -5882,7 +5576,7 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>JD_THC19 : CBD1</t>
+          <t>JD_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
@@ -6266,7 +5960,7 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>OPM_THC21 : CBD1</t>
+          <t>OPM_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
@@ -6445,7 +6139,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -6481,7 +6175,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -6521,7 +6215,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -7095,7 +6789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7118,7 +6812,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Nominal potency of every grade is a whole EVEN number (…8, 10, 12 … 26), printed in the product code as THCnn : CBD1 and shown on the specification as nn.00 %.</t>
+          <t>MANDATORY product codes (management, 27.08.2026): the 48 tranche-list batches carry exactly the THCnn : CBD1 codes management assigned. The solver treats them as fixed constraints; a deviation is permitted only where the assigned codes are mutually impossible under rules 2-4, is minimal (fewest batches moved), and is flagged. Result: 46/48 honored; 2 unavoidable deviations (CJ062501/1 21.51: THC22-&gt;THC20 beside the mandatory THC24 holding 22.30; PM112501 audited 13.33 &gt; 13.20 ceiling of THC12 -&gt; THC14). Uncoded batches take any feasible even nominal — the nominal is NOT chased after the analysis value; odd only where no even configuration exists.</t>
         </is>
       </c>
     </row>
@@ -7130,7 +6824,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>A grade range never extends more than 10% of the nominal to either side (lower &gt;= 0.90 x nominal, upper &lt;= 1.10 x nominal). Bounds carry two decimals.</t>
+          <t>SYMMETRIC tolerance: every grade is nominal ± t with the SAME t above and below (window centred on the nominal), t at most 10% of the nominal, bounds two decimals, minimum meaningful tolerance 0.50.</t>
         </is>
       </c>
     </row>
@@ -7142,7 +6836,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SYMMETRIC tolerance (management rule, 27.08.2026): every grade is nominal ± t with the SAME t above and below, so the window is always centred on the nominal. Contiguity then binds neighbouring grades by the equality t_upper + t_lower = (N_upper - N_lower) - 0.01, which chains every tolerance to the top grade of the ladder.</t>
+          <t>NO EMPTY GRADES (management rule, 27.08.2026): every grade holds at least one tested batch. Where real grades cannot reach each other under the 10% cap, the result-free span between them stays as a DOCUMENTED GAP — never as an empty reserve grade.</t>
         </is>
       </c>
     </row>
@@ -7154,7 +6848,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ranges within one strain do not overlap; the strongest grade is given the maximum tolerance the chain allows first, each weaker grade takes what the equalities leave.</t>
+          <t>BALANCED distribution (management rule, 27.08.2026): where two grades touch, the shared budget (nominal difference − 0.01) is split as EQUALLY as the batch-containment and 10% constraints allow — no grade is squeezed for the benefit of its neighbour. Grades touch wherever the mathematics permits; a grade facing a gap takes its maximum coverage.</t>
         </is>
       </c>
     </row>
@@ -7166,7 +6860,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Every batch of the strain falls inside exactly one grade window at its latest certified Total THC value (retest = CoQ-forming; superseded pre-retest results are out of scope).</t>
+          <t>Every batch falls in exactly one grade at its latest certified value (retest = CoQ-forming; superseded pre-retest results are out of specification scope).</t>
         </is>
       </c>
     </row>
@@ -7178,33 +6872,33 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Contiguity: from the top grade down, consecutive ranges join at 0.01. RESERVE grades (spec-defined, no current batch) close spans that batch-bearing grades cannot bridge. Sole exception below 10% THC where no meaningful symmetric ladder joins: the lowest grade(s) sit with a documented uncovered zone (GRC 7.71-10.79; OPM 8.81-9.10).</t>
+          <t>Gaps carry no results by construction (each gap lies between the windows of grades that jointly contain every result of the strain); typical at the very lowest grades (GRC 7.71-10.79; OPM 8.81-8.99) and in result-free mid-spans (CJ, CC, FB, GP, JD, OPM). A future result landing in a gap triggers a grade-set revision, not an ad-hoc stretch.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>ODD-nominal adjustment (management rule, 27.08.2026): where the initially selected even nominal cannot carry a symmetric window under rules 2-6, the nominal shifts to the adjacent odd whole number (above or below). Also covers isolated results in the even ladder dead zones (GRC_THC7). No grade tolerance is allowed below 0.50 (a 0.40pp-wide grade is not a meaningful specification).</t>
-        </is>
-      </c>
+      <c r="A8" s="14" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr"/>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>FLAGS</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>FLAGS</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Cap Junky / CJ062501/1: MANDATORY-CODE DEVIATION (unavoidable) — THC22 for 21.51 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC20</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -7214,7 +6908,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky: THC22 -&gt; THC21 (odd shift for symmetric tolerance) [owner-coded]: CJ062501/1</t>
+          <t>Cap Junky: THC14 -&gt; THC16 (even re-nominal, distribution rule): CJ052501/02</t>
         </is>
       </c>
     </row>
@@ -7226,7 +6920,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky: THC20 -&gt; THC19 (odd shift for symmetric tolerance) [owner-coded]: CJ062501/2, CJ082501/2</t>
+          <t>Fat Bastard: THC20 -&gt; THC22 (even re-nominal, distribution rule): FB012603</t>
         </is>
       </c>
     </row>
@@ -7238,7 +6932,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky: THC14 -&gt; THC15 (odd shift for symmetric tolerance): CJ052501/02</t>
+          <t>Graps &amp; Creme / GRC102501/1: 7.05 fits no even nominal (even-ladder dead zone) -&gt; ODD fallback THC7 [6.30-7.70]</t>
         </is>
       </c>
     </row>
@@ -7250,33 +6944,21 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard: THC20 -&gt; THC21 (odd shift for symmetric tolerance): FB012603</t>
+          <t>Permanent Marker / PM112501: owner code THC12 infeasible for 13.33 (max window 10.80-13.20) -&gt; THC14</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Grape Pie: THC24 -&gt; THC25 (odd shift for symmetric tolerance) [owner-coded]: P160012, GP092501, P160022, GP0824_03, GP062501, P160032, GP0824_02</t>
-        </is>
-      </c>
+      <c r="A15" s="14" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Graps &amp; Creme / GRC102501/1: 7.05 fits no even nominal (even-ladder dead zone) -&gt; ODD fallback THC7 [6.30-7.70]</t>
-        </is>
-      </c>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>EXCEPTIONS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -7286,7 +6968,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz: THC20 -&gt; THC19 (odd shift for symmetric tolerance) [owner-coded]: JD012603/02, JD112501, JD022601, JD012601*</t>
+          <t>Cap Junky: uncovered zone 17.61-17.99 between THC20 and THC16 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7298,7 +6980,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa: THC22 -&gt; THC21 (odd shift for symmetric tolerance) [owner-coded]: OPM1024</t>
+          <t>Cash Cow: uncovered zone 15.00-16.19 between THC18 and THC14 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7310,21 +6992,33 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Permanent Marker / PM112501: owner code THC12 infeasible for 13.33 (max window 10.80-13.20) -&gt; THC14</t>
+          <t>Fat Bastard: uncovered zone 15.00-16.19 between THC18 and THC14 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Grape Pie: uncovered zone 21.37-21.59 between THC24 and THC20 (result-free span — no result on file; no-empty-grades rule)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>EXCEPTIONS</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme: uncovered zone 7.71-10.79 between THC12 and THC7 (sub-10% territory — no result on file; no-empty-grades rule)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -7334,7 +7028,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme: uncovered zone 7.71-10.79 between THC12 and THC7 (sub-10% territory — ladder cannot join symmetrically; permitted per rule)</t>
+          <t>Jelly Donutz: uncovered zone 17.00-17.99 between THC20 and THC16 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7346,45 +7040,45 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa: uncovered zone 8.81-9.10 between THC10 and THC8 (sub-10% territory — ladder cannot join symmetrically; permitted per rule)</t>
+          <t>Orange Punch Mimosa: uncovered zone 19.01-19.79 between THC22 and THC18 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr"/>
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa: uncovered zone 11.01-12.99 between THC14 and THC10 (result-free span — no result on file; no-empty-grades rule)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa: uncovered zone 8.81-8.99 between THC10 and THC8 (sub-10% territory — no result on file; no-empty-grades rule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>OPEN VERIFICATIONS CARRIED OVER</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
-        </is>
-      </c>
+      <c r="B27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -7394,7 +7088,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
+          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7100,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7112,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7124,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Truth-check finding (27.08.2026): certificate ППК26065 (13.93, CNP, 11.05.2026) prints серија JD112501* — the milled Jelly Donutz presentation, a separate register batch — and was misattributed to JD112501 (whole flower, retest 20.32) in the source dataset. Reattributed; JD112501* now carries its own grade JD_THC14:CBD1 (12.60 — 14.39).</t>
+          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
         </is>
       </c>
     </row>
@@ -7441,6 +7135,30 @@
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Truth-check finding (27.08.2026): certificate ППК26065 (13.93, CNP, 11.05.2026) prints серија JD112501* — the milled Jelly Donutz presentation, a separate register batch — and was misattributed to JD112501 (whole flower, retest 20.32) in the source dataset. Reattributed; JD112501* now carries its own grade JD_THC14:CBD1 (12.60 — 14.39).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Batches on declared values (no eCoA yet): ACC102501, CC012603, CF102501, JD012603/01, PUM102501 (T2 re-analysis sampled 12.08.2026, results pending), SCR012601, WED102501, JD022601, GRC102501/1, P160012, P160022, P160032 — their grades are provisional.</t>
         </is>

--- a/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
+++ b/deliverables/potency_study/ImB_Potency_Grade_Ranges.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ImB POTENCY GRADE RANGES — EVEN WHOLE-NUMBER NOMINALS (proposal 27.08.2026)</t>
+          <t>ImB POTENCY GRADE RANGES — EVEN WHOLE-NUMBER NOMINALS (proposal 27.08.2026, rev. 2 — T1+T2 re-analysis anchors of 26.08.2026)</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>ACC102501 12.91</t>
+          <t>ACC102501 12.09</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>BSS052501 20.39</t>
+          <t>BSS052501 20.52</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC24 : CBD1</t>
+          <t>CJ_THC28 : CBD1</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>±1.99</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>22.01</v>
+        <v>27</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>25.99</v>
+        <v>29</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>3.98</v>
+        <v>2</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>24.00% ±1.99% (22.01% — 25.99%)</t>
+          <t>28.00% ±1.00% (27.00% — 29.00%)</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>CJ082501/1 24.96, CJ052501/01 24.05, CJ072501 23.70, CJ1024 23.00, CJ092501 22.30</t>
+          <t>CJ082501/1 28.34</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC20 : CBD1</t>
+          <t>CJ_THC26 : CBD1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -961,35 +961,35 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>±2.00</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>18</v>
+        <v>25.01</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>22</v>
+        <v>26.99</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>4</v>
+        <v>1.98</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>20.00% ±2.00% (18.00% — 22.00%)</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>26.00% ±0.99% (25.01% — 26.99%)</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>CJ062501/1 21.51, CJ062501/2 18.91, CJ082501/2 18.29</t>
+          <t>CJ092501 25.65</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CJ_THC16 : CBD1</t>
+          <t>CJ_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1012,94 +1012,86 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>±1.60</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>14.4</v>
+        <v>23</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
+          <t>24.00% ±1.00% (23.00% — 25.00%)</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>CJ062501/1 24.80, CJ052501/01 24.05, CJ072501 23.70, CJ1024 23.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>CJ_THC20 : CBD1</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CJ-IV</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>±2.00</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>20.00% ±2.00% (18.00% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>CJ052501/02 14.93</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Cash Cow</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>CC_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC-I</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>±1.80</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>CC012601/1 17.67</t>
+          <t>CJ062501/2 18.91, CJ082501/2 18.29</t>
         </is>
       </c>
     </row>
@@ -1108,149 +1100,149 @@
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>CJ_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CJ-V</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>±1.60</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>CJ052501/02 14.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CC_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CC-I</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>±1.80</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>CC012601/1 17.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>CC_THC14 : CBD1</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_CC-II</t>
         </is>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F16" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>±0.99</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>13.01</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>14.00% ±0.99% (13.01% — 14.99%)</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>CC112501 13.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>CC_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CC-III</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>±1.00</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>12.00% ±1.00% (11.00% — 13.00%)</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>CC012603 12.32</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Chem Flyer</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>CF_THC10 : CBD1</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_CF-I</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>±1.00</t>
+          <t>±1.40</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>11</v>
+        <v>15.4</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+          <t>14.00% ±1.40% (12.60% — 15.40%)</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -1260,19 +1252,19 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>CF102501 9.83</t>
+          <t>CC012603 14.76, CC112501 13.35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1282,34 +1274,34 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>CLE_THC8 : CBD1</t>
+          <t>CF_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_CLE-I</t>
+          <t>QCSP_001_CF-I</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>±0.80</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
@@ -1319,117 +1311,125 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>CLE072501 8.02</t>
+          <t>CF102501 9.55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CLE_THC8 : CBD1</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_CLE-I</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>±0.80</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>8.00% ±0.80% (7.20% — 8.80%)</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>CLE072501 8.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>FB_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>FB_THC20 : CBD1</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_FB-I</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>±2.19</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>19.81</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>24.19</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="F19" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>±1.14</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>20.00% ±1.14% (18.86% — 21.14%)</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>balanced (shared budget)</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>FB012603 20.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>FB_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_FB-II</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>±1.80</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>FB012602 18.86, FB012603V 18.29, FB112501 16.69</t>
+          <t>FB012603 20.83, FB012602 18.86</t>
         </is>
       </c>
     </row>
@@ -1438,39 +1438,39 @@
       <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>FB_THC14 : CBD1</t>
+          <t>FB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-III</t>
+          <t>QCSP_001_FB-II</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>±0.99</t>
+          <t>±0.85</t>
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>13.01</v>
+        <v>17.15</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>14.99</v>
+        <v>18.85</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±0.99% (13.01% — 14.99%)</t>
+          <t>18.00% ±0.85% (17.15% — 18.85%)</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>FB012601/1 14.68</t>
+          <t>FB012603V 18.29, FB012601/1 17.99</t>
         </is>
       </c>
     </row>
@@ -1489,149 +1489,149 @@
       <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>FB_THC16 : CBD1</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_FB-III</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>±1.14</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>16.00% ±1.14% (14.86% — 17.14%)</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>FB112501 16.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>FB_THC12 : CBD1</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_FB-IV</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F22" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>±1.00</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>12.00% ±1.00% (11.00% — 13.00%)</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>±1.20</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>12.00% ±1.20% (10.80% — 13.20%)</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>FB032601 12.39</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>GG</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>GG_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_GG-I</t>
         </is>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F23" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>±1.00</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.00% (17.00% — 19.00%)</t>
-        </is>
-      </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>GG_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GG-II</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>16</v>
-      </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
           <t>±0.99</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>15.01</v>
+        <v>17.01</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>16.99</v>
+        <v>18.99</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>1.98</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±0.99% (15.01% — 16.99%)</t>
+          <t>18.00% ±0.99% (17.01% — 18.99%)</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>GG012603 16.70, GG1024_02 15.95, GG012601* 15.35</t>
+          <t>GG032601 18.98, GG1024_01 18.67, GG112501 17.94</t>
         </is>
       </c>
     </row>
@@ -1650,21 +1650,21 @@
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>GG_THC14 : CBD1</t>
+          <t>GG_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-III</t>
+          <t>QCSP_001_GG-II</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
@@ -1672,17 +1672,17 @@
         </is>
       </c>
       <c r="H24" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
+          <t>16.00% ±1.00% (15.00% — 17.00%)</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>GG1024 13.34</t>
+          <t>GG012603 16.70, GG1024_02 15.95, GG1024 15.51, GG012601* 15.35</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC28 : CBD1</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1723,35 +1723,35 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>±2.40</t>
+          <t>±1.39</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>21.6</v>
+        <v>26.61</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>26.4</v>
+        <v>29.39</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>24.00% ±2.40% (21.60% — 26.40%)</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>28.00% ±1.39% (26.61% — 29.39%)</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>P160012 26.32, GP092501 25.73, P160022 25.72, GP0824_03 25.45, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
+          <t>GP0824_03 28.03</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>GP_THC20 : CBD1</t>
+          <t>GP_THC26 : CBD1</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1774,25 +1774,25 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>±1.36</t>
+          <t>±0.60</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>18.64</v>
+        <v>25.4</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>21.36</v>
+        <v>26.6</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>2.72</v>
+        <v>1.2</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>20.00% ±1.36% (18.64% — 21.36%)</t>
+          <t>26.00% ±0.60% (25.40% — 26.60%)</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>GP072501/1 21.36, GP082501/1 21.29, GP0824_01 20.79, GP072501/2 19.81</t>
+          <t>P160012 26.32, P160022 25.72</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>GP_THC18 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1825,25 +1825,25 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>±0.63</t>
+          <t>±1.39</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>17.37</v>
+        <v>22.61</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>18.63</v>
+        <v>25.39</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.26</v>
+        <v>2.78</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±0.63% (17.37% — 18.63%)</t>
+          <t>24.00% ±1.39% (22.61% — 25.39%)</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>GP052501 18.52</t>
+          <t>GP092501 25.24, GP082501/1 25.13, GP062501 24.89, P160032 24.78, GP0824_02 22.61</t>
         </is>
       </c>
     </row>
@@ -1867,291 +1867,283 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>GP_THC20 : CBD1</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_GP-IV</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>±2.00</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>20.00% ±2.00% (18.00% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>GP072501/1 21.36, GP0824_01 20.79, GP052501 18.52, GP072501/2 18.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
           <t>GP_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GP-IV</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_GP-V</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>±1.36</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>17.36</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>16.00% ±1.36% (14.64% — 17.36%)</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>±1.60</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>GP082501/2 15.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>GRC_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_GRC-I</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>GRC102501/2 9.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>GRC_THC7 : CBD1</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_GRC-II</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>±0.70</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>7.00% ±0.70% (6.30% — 7.70%)</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>GRC102501/1 7.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>HPA</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>HPA_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_HPA-I</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±1.00% (21.00% — 23.00%)</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>balanced (shared budget)</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>GP082501/2 15.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Graps &amp; Creme</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>GRC</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>GRC_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GRC-I</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>±1.20</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>12.00% ±1.20% (10.80% — 13.20%)</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>GRC102501/2 11.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr"/>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>HPA1024_01 21.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>GRC_THC7 : CBD1</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_GRC-II</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>±0.70</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>7.00% ±0.70% (6.30% — 7.70%)</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10% — ODD nominal (fallback rule 5)</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>GRC102501/1 7.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>High Pro Amnesia</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>HPA</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>HPA_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_HPA-I</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>±2.19</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>19.81</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>24.19</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>HPA1024_01 21.61, HPA052501 20.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr"/>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>HPA_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>HPA_THC20 : CBD1</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_HPA-II</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>±1.80</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>HPA1024 17.31</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Jelly Donutz</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>JD_THC20 : CBD1</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_JD-I</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -2159,31 +2151,31 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>±2.00</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>18</v>
+        <v>19.01</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>22</v>
+        <v>20.99</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>4</v>
+        <v>1.98</v>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>20.00% ±2.00% (18.00% — 22.00%)</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>20.00% ±0.99% (19.01% — 20.99%)</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>JD012603/02 20.54, JD112501 20.32, JD022601 18.58, JD012601* 18.16</t>
+          <t>HPA052501 19.69</t>
         </is>
       </c>
     </row>
@@ -2192,159 +2184,159 @@
       <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>HPA_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_HPA-III</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.00% (17.00% — 19.00%)</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>HPA1024 17.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>JD_THC20 : CBD1</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_JD-I</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>±2.00</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>20.00% ±2.00% (18.00% — 22.00%)</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>JD012603/01 21.01, JD112501 20.32, JD022601 18.58, JD012601* 18.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>JD_THC16 : CBD1</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_JD-II</t>
         </is>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F36" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>±0.99</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>15.01</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>16.00% ±0.99% (15.01% — 16.99%)</t>
-        </is>
-      </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>±1.09</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>16.00% ±1.09% (14.91% — 17.09%)</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>balanced (shared budget)</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr">
-        <is>
-          <t>JD012603/01 16.71, JD012603/02V 15.16</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>JD_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_JD-III</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>±1.00</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>JD112501* 13.93</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>J31</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>J31_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_J31-I</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>±2.19</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>19.81</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>24.19</v>
-      </c>
-      <c r="J36" s="6" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
-        </is>
-      </c>
-      <c r="L36" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>J31122501 21.84, J31112501 20.21</t>
+          <t>JD012603/02V 17.09</t>
         </is>
       </c>
     </row>
@@ -2353,61 +2345,61 @@
       <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>J31_THC18 : CBD1</t>
+          <t>JD_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_J31-II</t>
+          <t>QCSP_001_JD-III</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>±1.80</t>
+          <t>±0.90</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>16.2</v>
+        <v>13.1</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>19.8</v>
+        <v>14.9</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>14.00% ±0.90% (13.10% — 14.90%)</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>J31102501 17.32</t>
+          <t>JD012603/02 14.43, JD112501* 13.93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>J31</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2417,71 +2409,63 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>KC_THC18 : CBD1</t>
+          <t>J31_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_KC-I</t>
+          <t>QCSP_001_J31-I</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>±1.80</t>
+          <t>±2.19</t>
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>16.2</v>
+        <v>19.81</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>19.8</v>
+        <v>24.19</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3.6</v>
+        <v>4.38</v>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
+          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>KC102501 17.04</t>
+          <t>J31122501 21.84, J31112501 20.21</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Motor Breath</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
+      <c r="A39" s="7" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>MB_THC18 : CBD1</t>
+          <t>J31_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-I</t>
+          <t>QCSP_001_J31-II</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -2489,192 +2473,208 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>±0.99</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>17.01</v>
+        <v>16.2</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>18.99</v>
+        <v>19.8</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>18.00% ±0.99% (17.01% — 18.99%)</t>
-        </is>
-      </c>
-      <c r="L39" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>MB0824_04 18.67</t>
+          <t>J31102501 17.32</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr"/>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>MB_THC16 : CBD1</t>
+          <t>KC_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_MB-II</t>
+          <t>QCSP_001_KC-I</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>±1.00</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H40" s="6" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>17</v>
+        <v>19.8</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±1.00% (15.00% — 17.00%)</t>
-        </is>
-      </c>
-      <c r="L40" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>MB0824_05 16.82</t>
+          <t>KC102501 17.06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>MB_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_MB-I</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>±1.80</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>MB0824_04 18.67, MB0824_05 17.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>OPM</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>OPM_THC22 : CBD1</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>QCSP_001_OPM-I</t>
         </is>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F42" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>±2.20</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>±2.19</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>OPM1024 20.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr"/>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>OPM_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_OPM-II</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>±1.00</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.00% (17.00% — 19.00%)</t>
-        </is>
-      </c>
-      <c r="L42" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="inlineStr">
-        <is>
-          <t>OPM1024_02 18.04</t>
         </is>
       </c>
     </row>
@@ -2683,49 +2683,49 @@
       <c r="B43" s="5" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-III</t>
+          <t>QCSP_001_OPM-II</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>±0.99</t>
+          <t>±1.80</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>15.01</v>
+        <v>16.2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>16.99</v>
+        <v>19.8</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±0.99% (15.01% — 16.99%)</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>OPM1024_03 16.55, OMP1024_01 15.38</t>
+          <t>OPM1024_03 19.30, OMP1024_01 18.99, OPM1024_02 18.04</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       <c r="B44" s="5" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-IV</t>
+          <t>QCSP_001_OPM-III</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -2752,26 +2752,26 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>±1.00</t>
+          <t>±1.40</t>
         </is>
       </c>
       <c r="H44" s="6" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
-        </is>
-      </c>
-      <c r="L44" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
+          <t>14.00% ±1.40% (12.60% — 15.40%)</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -2785,7 +2785,7 @@
       <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-V</t>
+          <t>QCSP_001_OPM-IV</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>OPM092501 9.43</t>
+          <t>OPM092501 10.18</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       <c r="B46" s="5" t="inlineStr"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-VI</t>
+          <t>QCSP_001_OPM-V</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>PM_THC14 : CBD1</t>
+          <t>PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2909,25 +2909,25 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>±1.00</t>
+          <t>±0.99</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>13</v>
+        <v>11.01</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>15</v>
+        <v>12.99</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>14.00% ±1.00% (13.00% — 15.00%)</t>
+          <t>12.00% ±0.99% (11.01% — 12.99%)</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>PM112501 13.33</t>
+          <t>PM092501 12.25</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>PM_THC12 : CBD1</t>
+          <t>PM_THC10 : CBD1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -2960,76 +2960,84 @@
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>±0.99</t>
+          <t>±1.00</t>
         </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>11.01</v>
+        <v>9</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>12.99</v>
+        <v>11</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>12.00% ±0.99% (11.01% — 12.99%)</t>
-        </is>
-      </c>
-      <c r="L48" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>PM092501 12.25</t>
+          <t>PM112501 10.79, PM072501 10.01</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr"/>
-      <c r="B49" s="5" t="inlineStr"/>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>PUM</t>
+        </is>
+      </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>PM_THC10 : CBD1</t>
+          <t>PUM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-III</t>
+          <t>QCSP_001_PUM-I</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>±1.00</t>
+          <t>±1.40</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>11</v>
+        <v>15.4</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+          <t>14.00% ±1.40% (12.60% — 15.40%)</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
@@ -3039,19 +3047,19 @@
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>PM072501 10.01</t>
+          <t>PUM102501 13.95</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>PUM</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3061,276 +3069,276 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>PUM_THC16 : CBD1</t>
+          <t>SCR_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_PUM-I</t>
+          <t>QCSP_001_SCR-I</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>±1.60</t>
+          <t>±2.19</t>
         </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>14.4</v>
+        <v>19.81</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>17.6</v>
+        <v>24.19</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>16.00% ±1.60% (14.40% — 17.60%)</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
+          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>SCR022601 21.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr"/>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>SCR_THC18 : CBD1</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SCR-II</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>±1.80</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="M50" s="7" t="inlineStr">
-        <is>
-          <t>PUM102501 15.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>SCR</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>SCR112501 19.73, SCR012601 18.07, SCR012603 17.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>SCR_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SCR-I</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="n">
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>SJ_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SJ-I</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>±0.99</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>12.00% ±0.99% (11.01% — 12.99%)</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>balanced (shared budget)</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>SJ102501 11.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>SJ_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_SJ-II</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>±1.00</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>FULL ±10%</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>SJ092501 10.39, SJ112501 9.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>WED</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>WED_THC22 : CBD1</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>QCSP_001_WED-I</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>±2.19</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>19.81</v>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>24.19</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.19% (19.81% — 24.19%)</t>
-        </is>
-      </c>
-      <c r="L51" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>SCR022601 21.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr"/>
-      <c r="B52" s="5" t="inlineStr"/>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>SCR_THC18 : CBD1</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SCR-II</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>±1.80</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I52" s="6" t="n">
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>±2.20</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="n">
         <v>19.8</v>
       </c>
-      <c r="J52" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>18.00% ±1.80% (16.20% — 19.80%)</t>
-        </is>
-      </c>
-      <c r="L52" s="8" t="inlineStr">
+      <c r="I54" s="6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
         <is>
           <t>FULL ±10%</t>
         </is>
       </c>
-      <c r="M52" s="7" t="inlineStr">
-        <is>
-          <t>SCR012601 18.07, SCR012603 17.84, SCR112501 17.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Sleepy Joy</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>SJ_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SJ-I</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>±0.99</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>12.00% ±0.99% (11.01% — 12.99%)</t>
-        </is>
-      </c>
-      <c r="L53" s="9" t="inlineStr">
-        <is>
-          <t>balanced (shared budget)</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>SJ102501 11.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr"/>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>SJ_THC10 : CBD1</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_SJ-II</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>±1.00</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
-        <is>
-          <t>10.00% ±1.00% (9.00% — 11.00%)</t>
-        </is>
-      </c>
-      <c r="L54" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>SJ092501 10.96, SJ112501 9.20</t>
+          <t>WED102501 22.05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>WED</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3340,12 +3348,12 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>WED_THC22 : CBD1</t>
+          <t>WC_THC22 : CBD1</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>QCSP_001_WED-I</t>
+          <t>QCSP_001_WC-I</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3377,66 +3385,7 @@
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>WED102501 22.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Wedding Crasher</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>WC</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>WC_THC22 : CBD1</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>QCSP_001_WC-I</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>±2.20</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
-        <is>
-          <t>22.00% ±2.20% (19.80% — 24.20%)</t>
-        </is>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>FULL ±10%</t>
-        </is>
-      </c>
-      <c r="M56" s="7" t="inlineStr">
-        <is>
-          <t>WC072501 22.11, WC082501 21.67</t>
+          <t>WC082501 23.48, WC072501 22.11</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3477,11 @@
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>12.91</v>
+        <v>12.09</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -3542,7 +3491,7 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
@@ -3720,11 +3669,11 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>20.39</v>
+        <v>20.52</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>In-house GC cross-check NGP/QCG/SOP-024, 28.11.2025, PP</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3732,7 +3681,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3752,15 +3705,15 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC24 : CBD1</t>
+          <t>CJ_THC28 : CBD1</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>24.96</v>
+        <v>28.34</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>ППК26002, 21.01.2026, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3768,12 +3721,16 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>CJ052501/01</t>
+          <t>CJ092501</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -3783,20 +3740,20 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC24 : CBD1</t>
+          <t>CJ_THC26 : CBD1</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>24.05</v>
+        <v>25.65</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>197-3-К/26, 07.08.2026, FARM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -3804,12 +3761,16 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>CJ072501</t>
+          <t>CJ062501/1</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3819,7 +3780,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3828,28 +3789,28 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>ППК25367, 28.11.2025, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>CJ1024</t>
+          <t>CJ052501/01</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -3859,7 +3820,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3868,28 +3829,24 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>23</v>
+        <v>24.05</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>ППК25052, 26.02.2025, UKIM</t>
+          <t>197-3-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>CJ092501</t>
+          <t>CJ072501</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3899,7 +3856,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3908,24 +3865,28 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>22.3</v>
+        <v>23.7</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>ППК26007, 21.01.2026, UKIM</t>
+          <t>ППК25367, 28.11.2025, UKIM</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>CJ062501/1</t>
+          <t>CJ1024</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -3935,28 +3896,32 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>CJ_THC20 : CBD1</t>
+          <t>CJ_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>21.51</v>
+        <v>23</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>ППК25321, 23.10.2025, UKIM</t>
+          <t>ППК25052, 26.02.2025, UKIM</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3971,7 +3936,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -4011,7 +3976,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -4047,7 +4012,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -4117,7 +4082,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>CC012603</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -4136,28 +4101,28 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>13.35</v>
+        <v>14.76</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>ППК26068, 11.05.2026, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>CC012603</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4167,30 +4132,30 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>CC_THC12 : CBD1</t>
+          <t>CC_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>12.32</v>
+        <v>13.35</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>ППК26068, 11.05.2026, UKIM</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>code assigned by value (batch not on the tranche list)</t>
         </is>
       </c>
     </row>
@@ -4216,11 +4181,11 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>9.83</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -4230,7 +4195,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
@@ -4256,11 +4221,11 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>8.02</v>
+        <v>8.65</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>PP CoA #027 / ППК25370, 21.01.2026, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -4268,7 +4233,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -4288,7 +4257,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>FB_THC22 : CBD1</t>
+          <t>FB_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
@@ -4323,12 +4292,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>FB_THC18 : CBD1</t>
+          <t>FB_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
@@ -4387,49 +4356,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>FB112501</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>FB012601/1</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>FB_THC18 : CBD1</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
-        <v>16.69</v>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>ППК26066, 11.05.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+      <c r="E25" s="12" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>owner code THC16 infeasible for 17.99 (max window 14.40-17.60) -&gt; THC18 — infeasible, deviation flagged</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>FB012601/1</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -4444,23 +4413,27 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>FB_THC14 : CBD1</t>
+          <t>FB_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>14.68</v>
+        <v>16.69</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>ППК26067, 11.05.2026, UKIM</t>
+          <t>ППК26066, 11.05.2026, UKIM</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -4697,7 +4670,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GG012601*</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -4716,28 +4689,28 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>15.35</v>
+        <v>15.51</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>ППК26062, 11.05.2026, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>GG012601*</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -4747,33 +4720,37 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>GG_THC14 : CBD1</t>
+          <t>GG_THC16 : CBD1</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>13.34</v>
+        <v>15.35</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed), 23.04.2025, UKIM</t>
+          <t>ППК26062, 11.05.2026, UKIM</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>P160012</t>
+          <t>GP0824_03</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -4788,32 +4765,32 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC28 : CBD1</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>26.32</v>
+        <v>28.03</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>ППК26117, 06.07.2026, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>GP092501</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -4823,28 +4800,32 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC26 : CBD1</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>25.73</v>
+        <v>26.32</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>ППК26009, 21.01.2026, UKIM</t>
+          <t>ППК26117, 06.07.2026, UKIM</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -4859,12 +4840,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC26 : CBD1</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
@@ -4887,85 +4868,89 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>GP0824_03</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>GP092501</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
-        <v>25.45</v>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>ППК25175, 10.07.2025, UKIM</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="E38" s="12" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr"/>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>MANDATORY-CODE DEVIATION (unavoidable) — THC26 for 25.24 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC24 — infeasible, deviation flagged</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>GP062501</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>GP082501/1</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>GP_THC24 : CBD1</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
-        <v>24.89</v>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024, 28.11.2025, PP</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+      <c r="E39" s="12" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>MANDATORY-CODE DEVIATION (unavoidable) — THC26 for 25.13 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC24 — infeasible, deviation flagged</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>GP062501</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -4975,7 +4960,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -4984,11 +4969,11 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>24.78</v>
+        <v>24.89</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, UKIM</t>
+          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024, 28.11.2025, PP</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -5005,7 +4990,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>GP0824_02</t>
+          <t>P160032</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -5015,7 +5000,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -5024,24 +5009,28 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>22.61</v>
+        <v>24.78</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>197-11-К/26, 07.08.2026, FARM</t>
+          <t>ППК26119, 06.07.2026, UKIM</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>GP072501/1</t>
+          <t>GP0824_02</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -5051,37 +5040,33 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>GP_THC20 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>21.36</v>
+        <v>22.61</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>PP CoA #018 / ППК25378, 21.01.2026, UKIM</t>
+          <t>197-11-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>GP082501/1</t>
+          <t>GP072501/1</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -5091,7 +5076,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -5100,19 +5085,23 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>21.29</v>
+        <v>21.36</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>PP CoA #020 / ППК25380, 21.01.2026, UKIM</t>
+          <t>PP CoA #018 / ППК25378, 21.01.2026, UKIM</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -5127,7 +5116,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -5157,7 +5146,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>GP072501/2</t>
+          <t>GP052501</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -5167,7 +5156,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -5176,11 +5165,11 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>19.81</v>
+        <v>18.52</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>PP CoA #019 / ППК25379, 21.01.2026, UKIM</t>
+          <t>197-10-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -5193,7 +5182,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>GP052501</t>
+          <t>GP072501/2</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -5203,20 +5192,20 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>GP_THC18 : CBD1</t>
+          <t>GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>18.52</v>
+        <v>18.29</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>197-10-К/26, 07.08.2026, FARM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -5224,7 +5213,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -5239,7 +5232,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -5263,40 +5256,44 @@
       <c r="H47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>GRC102501/2</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Graps &amp; Creme</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>GRC_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>11.53</v>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>051-6-K/26, 04.03.2026, FARM</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>GRC_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>owner code THC12 infeasible for 9.80 (max window 10.80-13.20) -&gt; THC10 — infeasible, deviation flagged</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -5387,20 +5384,20 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>HPA_THC22 : CBD1</t>
+          <t>HPA_THC20 : CBD1</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>20.39</v>
+        <v>19.69</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>ППК25278, 19.09.2025, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5408,7 +5405,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -5423,7 +5424,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -5449,7 +5450,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>JD012603/02</t>
+          <t>JD012603/01</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -5468,11 +5469,11 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>20.54</v>
+        <v>21.01</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5480,7 +5481,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -5601,7 +5606,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>JD012603/01</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -5620,11 +5625,11 @@
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>16.71</v>
+        <v>17.09</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5634,45 +5639,49 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>JD012603/02V</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>JD012603/02</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>JD_THC16 : CBD1</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>ППК26111, 30.06.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>JD_THC14 : CBD1</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr"/>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>owner code THC20 infeasible for 14.43 (max window 18.00-22.00) -&gt; THC14 — infeasible, deviation flagged</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -5852,11 +5861,11 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>17.04</v>
+        <v>17.06</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>051-4-K/26, 04.03.2026, FARM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -5864,7 +5873,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -5919,20 +5932,20 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>MB_THC16 : CBD1</t>
+          <t>MB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>16.82</v>
+        <v>17.93</v>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>ППК52211, 28.07.2025, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -5940,7 +5953,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -5981,7 +5998,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>OPM1024_02</t>
+          <t>OPM1024_03</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -6000,11 +6017,11 @@
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>18.04</v>
+        <v>19.3</v>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>197-18-К/26, 07.08.2026, FARM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -6012,12 +6029,16 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>OPM1024_03</t>
+          <t>OMP1024_01</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -6027,20 +6048,20 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>16.55</v>
+        <v>18.99</v>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>ППК25210, 28.07.2025, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -6048,12 +6069,16 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H68" s="7" t="inlineStr"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>OMP1024_01</t>
+          <t>OPM1024_02</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -6063,20 +6088,20 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>OPM_THC16 : CBD1</t>
+          <t>OPM_THC18 : CBD1</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>15.38</v>
+        <v>18.04</v>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>ППК25117, 06.05.2025, UKIM</t>
+          <t>197-18-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -6099,7 +6124,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -6139,7 +6164,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -6148,11 +6173,11 @@
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>9.43</v>
+        <v>10.18</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>ППК26008, 21.01.2026, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -6160,7 +6185,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -6175,7 +6204,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -6215,7 +6244,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -6239,80 +6268,80 @@
       <c r="H73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>PM092501</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>PM_THC12 : CBD1</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>197-20-К/26, 07.08.2026, FARM</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>PM112501</t>
         </is>
       </c>
-      <c r="B74" s="10" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>PM_THC14 : CBD1</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>ППК26030, 05.03.2026, UKIM</t>
-        </is>
-      </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>PM_THC10 : CBD1</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>owner code THC12 infeasible for audited 13.33 — moved to THC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>PM092501</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Permanent Marker</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>PM_THC12 : CBD1</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>197-20-К/26, 07.08.2026, FARM</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr"/>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>owner code THC12 infeasible for 10.79 (max window 10.80-13.20) -&gt; THC10 — infeasible, deviation flagged</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -6327,7 +6356,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -6372,15 +6401,15 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>PUM_THC16 : CBD1</t>
+          <t>PUM_THC14 : CBD1</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>15.63</v>
+        <v>13.95</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -6390,7 +6419,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
@@ -6437,7 +6466,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>SCR012601</t>
+          <t>SCR112501</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -6456,28 +6485,28 @@
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>18.07</v>
+        <v>19.73</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>owner-declared value</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>declared value — no eCoA yet, grade provisional until tested</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>SCR012601</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -6496,24 +6525,28 @@
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>17.84</v>
+        <v>18.07</v>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>197-21-К/26, 07.08.2026, FARM</t>
+          <t>owner-declared value</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>declared value — no eCoA yet, grade provisional until tested</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -6532,11 +6565,11 @@
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>17.13</v>
+        <v>17.84</v>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>ППК26069, 11.05.2026, UKIM</t>
+          <t>197-21-К/26, 07.08.2026, FARM</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -6608,11 +6641,11 @@
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>10.96</v>
+        <v>10.39</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>ППК26006, 21.01.2026, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -6620,7 +6653,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -6705,7 +6742,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>WC072501</t>
+          <t>WC082501</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -6724,28 +6761,28 @@
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>22.11</v>
+        <v>23.48</v>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>ППК25369, 28.11.2025, UKIM</t>
+          <t>Farmahem re-analysis, 26.08.2026 (unofficial — eCoA pending)</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>code assigned by value (batch not on the tranche list)</t>
+          <t>T2 re-analysis value 26.08.2026 (unofficial) — formal eCoA pending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>WC082501</t>
+          <t>WC072501</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -6764,19 +6801,23 @@
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>21.67</v>
+        <v>22.11</v>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>ППК26001, 21.01.2026, UKIM</t>
+          <t>ППК25369, 28.11.2025, UKIM</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>code assigned by value (batch not on the tranche list)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6789,7 +6830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6812,7 +6853,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MANDATORY product codes (management, 27.08.2026): the 48 tranche-list batches carry exactly the THCnn : CBD1 codes management assigned. The solver treats them as fixed constraints; a deviation is permitted only where the assigned codes are mutually impossible under rules 2-4, is minimal (fewest batches moved), and is flagged. Result: 46/48 honored; 2 unavoidable deviations (CJ062501/1 21.51: THC22-&gt;THC20 beside the mandatory THC24 holding 22.30; PM112501 audited 13.33 &gt; 13.20 ceiling of THC12 -&gt; THC14). Uncoded batches take any feasible even nominal — the nominal is NOT chased after the analysis value; odd only where no even configuration exists.</t>
+          <t>MANDATORY product codes (management, 27.08.2026 — revised with the 26.08.2026 T1+T2 re-analysis values): the 48 tranche-list batches carry exactly the THCnn : CBD1 codes management assigned. The solver treats them as fixed constraints; a deviation is permitted only where the assigned code is mathematically impossible under rules 2-4, is minimal (fewest batches moved), and is flagged. Result: 42/48 honored; 6 unavoidable deviations: FB012601/1 17.99 &gt; 17.60 ceiling of THC16 -&gt; THC18; GRC102501/2 9.80 &lt; 10.80 floor of THC12 -&gt; THC10; JD012603/02 14.43 far below the 18.00 floor of THC20 -&gt; THC14; PM112501 10.79 misses the 10.80 floor of THC12 by 0.01 -&gt; THC10; GP092501 25.24 and GP082501/1 25.13 coded THC26 cannot coexist with the mandatory THC24 holding GP0824_02 22.61 (no-overlap budget) -&gt; THC24. Uncoded batches take any feasible even nominal — the nominal is NOT chased after the analysis value; odd only where no even configuration exists.</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6901,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Every batch falls in exactly one grade at its latest certified value (retest = CoQ-forming; superseded pre-retest results are out of specification scope).</t>
+          <t>Every batch falls in exactly one grade at its CoQ-forming value: the 26.08.2026 T1+T2 re-analysis (Farmahem; T2 values unofficial until the formal eCoAs are filed), else the latest certificate, else the declared value. Retest = CoQ-forming (rule R5); superseded pre-retest results are out of specification scope.</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6913,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Gaps carry no results by construction (each gap lies between the windows of grades that jointly contain every result of the strain); typical at the very lowest grades (GRC 7.71-10.79; OPM 8.81-8.99) and in result-free mid-spans (CJ, CC, FB, GP, JD, OPM). A future result landing in a gap triggers a grade-set revision, not an ad-hoc stretch.</t>
+          <t>Gaps carry no results by construction (each gap lies between the windows of grades that jointly contain every result of the strain); typical at the very lowest grades (GRC 7.71-8.99; OPM 8.81-8.99) and in result-free mid-spans (CJ 22.01-22.99 &amp; 17.61-17.99; CC 15.41-16.19; FB 13.21-14.85; GP 22.01-22.60 &amp; 17.61-17.99; JD 17.10-17.99; OPM 15.41-16.19 &amp; 11.01-12.59). A future result landing in a gap triggers a grade-set revision, not an ad-hoc stretch.</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6937,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky / CJ062501/1: MANDATORY-CODE DEVIATION (unavoidable) — THC22 for 21.51 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC20</t>
+          <t>Cap Junky: THC14 -&gt; THC16 (even re-nominal, distribution rule): CJ052501/02</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6949,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky: THC14 -&gt; THC16 (even re-nominal, distribution rule): CJ052501/02</t>
+          <t>Fat Bastard / FB012601/1: owner code THC16 infeasible for 17.99 (max window 14.40-17.60) -&gt; THC18</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6961,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard: THC20 -&gt; THC22 (even re-nominal, distribution rule): FB012603</t>
+          <t>Fat Bastard / FB112501: uncoded batch re-joined — THC18 for 16.69 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC16</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6973,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme / GRC102501/1: 7.05 fits no even nominal (even-ladder dead zone) -&gt; ODD fallback THC7 [6.30-7.70]</t>
+          <t>Grape Pie / GP092501: MANDATORY-CODE DEVIATION (unavoidable) — THC26 for 25.24 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC24</t>
         </is>
       </c>
     </row>
@@ -6944,21 +6985,33 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Permanent Marker / PM112501: owner code THC12 infeasible for 13.33 (max window 10.80-13.20) -&gt; THC14</t>
+          <t>Grape Pie / GP082501/1: MANDATORY-CODE DEVIATION (unavoidable) — THC26 for 25.13 cannot coexist with the neighbouring mandatory grades (symmetric ±10%, no overlap) -&gt; THC24</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme / GRC102501/2: owner code THC12 infeasible for 9.80 (max window 10.80-13.20) -&gt; THC10</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>EXCEPTIONS</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme / GRC102501/1: 7.05 fits no even nominal (even-ladder dead zone) -&gt; ODD fallback THC7 [6.30-7.70]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -6968,7 +7021,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky: uncovered zone 17.61-17.99 between THC20 and THC16 (result-free span — no result on file; no-empty-grades rule)</t>
+          <t>Jelly Donutz / JD012603/02: owner code THC20 infeasible for 14.43 (max window 18.00-22.00) -&gt; THC14</t>
         </is>
       </c>
     </row>
@@ -6980,33 +7033,21 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cash Cow: uncovered zone 15.00-16.19 between THC18 and THC14 (result-free span — no result on file; no-empty-grades rule)</t>
+          <t>Permanent Marker / PM112501: owner code THC12 infeasible for 10.79 (max window 10.80-13.20) -&gt; THC10</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Fat Bastard: uncovered zone 15.00-16.19 between THC18 and THC14 (result-free span — no result on file; no-empty-grades rule)</t>
-        </is>
-      </c>
+      <c r="A19" s="14" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Grape Pie: uncovered zone 21.37-21.59 between THC24 and THC20 (result-free span — no result on file; no-empty-grades rule)</t>
-        </is>
-      </c>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>EXCEPTIONS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -7016,7 +7057,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme: uncovered zone 7.71-10.79 between THC12 and THC7 (sub-10% territory — no result on file; no-empty-grades rule)</t>
+          <t>Cap Junky: uncovered zone 22.01-22.99 between THC24 and THC20 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7069,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz: uncovered zone 17.00-17.99 between THC20 and THC16 (result-free span — no result on file; no-empty-grades rule)</t>
+          <t>Cap Junky: uncovered zone 17.61-17.99 between THC20 and THC16 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7081,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa: uncovered zone 19.01-19.79 between THC22 and THC18 (result-free span — no result on file; no-empty-grades rule)</t>
+          <t>Cash Cow: uncovered zone 15.41-16.19 between THC18 and THC14 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7093,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa: uncovered zone 11.01-12.99 between THC14 and THC10 (result-free span — no result on file; no-empty-grades rule)</t>
+          <t>Fat Bastard: uncovered zone 13.21-14.85 between THC16 and THC12 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7064,21 +7105,33 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa: uncovered zone 8.81-8.99 between THC10 and THC8 (sub-10% territory — no result on file; no-empty-grades rule)</t>
+          <t>Grape Pie: uncovered zone 22.01-22.60 between THC24 and THC20 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr"/>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Grape Pie: uncovered zone 17.61-17.99 between THC20 and THC16 (result-free span — no result on file; no-empty-grades rule)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>OPEN VERIFICATIONS CARRIED OVER</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr"/>
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme: uncovered zone 7.71-8.99 between THC10 and THC7 (sub-10% territory — no result on file; no-empty-grades rule)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -7088,7 +7141,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BSS052501: 20.39 (PP QCCoA 001v02) vs 20.47 on the owner sheet (unreadable NGP scan) — grade THC20 holds under either value; paper check pending.</t>
+          <t>Jelly Donutz: uncovered zone 17.10-17.99 between THC20 and THC16 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7153,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>OMP1024_01: 15.38 correction (cert ППК25117 prints 1.58 — printing anomaly) — VERIFY ON PAPER ORIGINAL; grade THC16 assumes 15.38.</t>
+          <t>Orange Punch Mimosa: uncovered zone 15.41-16.19 between THC18 and THC14 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7165,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
+          <t>Orange Punch Mimosa: uncovered zone 11.01-12.59 between THC14 and THC10 (result-free span — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
@@ -7124,33 +7177,21 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+          <t>Orange Punch Mimosa: uncovered zone 8.81-8.99 between THC10 and THC8 (sub-10% territory — no result on file; no-empty-grades rule)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
-        </is>
-      </c>
+      <c r="A32" s="14" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Truth-check finding (27.08.2026): certificate ППК26065 (13.93, CNP, 11.05.2026) prints серија JD112501* — the milled Jelly Donutz presentation, a separate register batch — and was misattributed to JD112501 (whole flower, retest 20.32) in the source dataset. Reattributed; JD112501* now carries its own grade JD_THC14:CBD1 (12.60 — 14.39).</t>
-        </is>
-      </c>
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>OPEN VERIFICATIONS CARRIED OVER</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -7160,7 +7201,79 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Batches on declared values (no eCoA yet): ACC102501, CC012603, CF102501, JD012603/01, PUM102501 (T2 re-analysis sampled 12.08.2026, results pending), SCR012601, WED102501, JD022601, GRC102501/1, P160012, P160022, P160032 — their grades are provisional.</t>
+          <t>The 29 Tranche-2 batches are graded on the 26.08.2026 Farmahem re-analysis values, which are UNOFFICIAL until the formal eCoAs are filed; those grades are provisional and the design re-runs automatically once the certificates arrive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Resolved by T2 (26.08.2026): the BSS052501 20.39-vs-20.47 discrepancy (now 20.52, THC20 holds), the OMP1024_01 ППК25117 printing anomaly (now 18.99 -&gt; THC18) and the PM112501 ППК26030 13.33-vs-13.00 question (now 10.79 -&gt; THC10) are all superseded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>GG1024_02: 15.95 correction (cert ППК25140 prints 15.59) — VERIFY ON PAPER ORIGINAL; grade THC16 holds under either value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>GP062501: PP cert prints 24.89 vs owner sheet 22.89 — grade THC24 holds under either value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>J31122501 graded on the machine-trimmed CoQ-forming preparation (21.84, CoQ-PP-2026-0054); the hand-trimmed 19.84 result is experimental only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Truth-check finding (27.08.2026): certificate ППК26065 (13.93, CNP, 11.05.2026) prints серија JD112501* — the milled Jelly Donutz presentation, a separate register batch — and was misattributed to JD112501 (whole flower, retest 20.32) in the source dataset. Reattributed; JD112501* carries its own grade JD_THC14:CBD1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Batches still on owner-declared values (no analysis on file): GRC102501/1 7.05, SCR012601 18.07, WED102501 22.05 — their grades are provisional.</t>
         </is>
       </c>
     </row>
